--- a/GameDesign/Excel/User.xlsx
+++ b/GameDesign/Excel/User.xlsx
@@ -725,7 +725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -737,7 +737,7 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
         <v>80</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="30" t="inlineStr"/>
     </row>
@@ -933,7 +933,7 @@
         <v>96</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="30" t="inlineStr"/>
     </row>
@@ -946,7 +946,7 @@
         <v>112</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="30" t="inlineStr"/>
     </row>
@@ -961,11 +961,7 @@
       <c r="D13" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="n"/>
@@ -976,7 +972,7 @@
         <v>160</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="30" t="inlineStr"/>
     </row>
@@ -989,7 +985,7 @@
         <v>192</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="30" t="inlineStr"/>
     </row>
@@ -1002,7 +998,7 @@
         <v>232</v>
       </c>
       <c r="D16" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="30" t="inlineStr"/>
     </row>
@@ -1015,7 +1011,7 @@
         <v>280</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="30" t="inlineStr"/>
     </row>
@@ -1030,11 +1026,7 @@
       <c r="D18" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E18" s="28" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="n"/>
@@ -1045,7 +1037,7 @@
         <v>408</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="30" t="inlineStr"/>
     </row>
@@ -1058,7 +1050,7 @@
         <v>488</v>
       </c>
       <c r="D20" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="30" t="inlineStr"/>
     </row>
@@ -1071,7 +1063,7 @@
         <v>592</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="30" t="inlineStr"/>
     </row>
@@ -1084,7 +1076,7 @@
         <v>712</v>
       </c>
       <c r="D22" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="30" t="inlineStr"/>
     </row>
@@ -1099,11 +1091,7 @@
       <c r="D23" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E23" s="28" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="30" t="n"/>
@@ -1114,7 +1102,7 @@
         <v>1024</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="30" t="inlineStr"/>
     </row>
@@ -1127,7 +1115,7 @@
         <v>1232</v>
       </c>
       <c r="D25" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="30" t="inlineStr"/>
     </row>
@@ -1140,7 +1128,7 @@
         <v>1472</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="30" t="inlineStr"/>
     </row>
@@ -1153,7 +1141,7 @@
         <v>1768</v>
       </c>
       <c r="D27" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="30" t="inlineStr"/>
     </row>
@@ -1168,11 +1156,7 @@
       <c r="D28" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E28" s="28" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="30" t="n"/>
@@ -1183,7 +1167,7 @@
         <v>2552</v>
       </c>
       <c r="D29" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="30" t="inlineStr"/>
     </row>
@@ -1196,7 +1180,7 @@
         <v>3064</v>
       </c>
       <c r="D30" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="30" t="inlineStr"/>
     </row>
@@ -1209,7 +1193,7 @@
         <v>3680</v>
       </c>
       <c r="D31" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="30" t="inlineStr"/>
     </row>
@@ -1222,7 +1206,7 @@
         <v>4416</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="30" t="inlineStr"/>
     </row>
@@ -1237,11 +1221,7 @@
       <c r="D33" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="30" t="n"/>
@@ -1252,7 +1232,7 @@
         <v>6352</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="30" t="inlineStr"/>
     </row>
@@ -1265,7 +1245,7 @@
         <v>7624</v>
       </c>
       <c r="D35" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="30" t="inlineStr"/>
     </row>
@@ -1278,7 +1258,7 @@
         <v>9152</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="30" t="inlineStr"/>
     </row>
@@ -1291,7 +1271,7 @@
         <v>10984</v>
       </c>
       <c r="D37" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="30" t="inlineStr"/>
     </row>
@@ -1306,11 +1286,7 @@
       <c r="D38" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E38" s="28" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="30" t="n"/>
@@ -1321,7 +1297,7 @@
         <v>15824</v>
       </c>
       <c r="D39" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="30" t="inlineStr"/>
     </row>
@@ -1334,7 +1310,7 @@
         <v>18984</v>
       </c>
       <c r="D40" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="30" t="inlineStr"/>
     </row>
@@ -1347,7 +1323,7 @@
         <v>22784</v>
       </c>
       <c r="D41" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="30" t="inlineStr"/>
     </row>
@@ -1360,7 +1336,7 @@
         <v>27344</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="30" t="inlineStr"/>
     </row>
@@ -1375,11 +1351,7 @@
       <c r="D43" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E43" s="28" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="30" t="n"/>
@@ -1390,7 +1362,7 @@
         <v>39376</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="30" t="inlineStr"/>
     </row>
@@ -1403,7 +1375,7 @@
         <v>47248</v>
       </c>
       <c r="D45" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="30" t="inlineStr"/>
     </row>
@@ -1416,7 +1388,7 @@
         <v>56704</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="30" t="inlineStr"/>
     </row>
@@ -1429,7 +1401,7 @@
         <v>68040</v>
       </c>
       <c r="D47" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="30" t="inlineStr"/>
     </row>
@@ -1444,11 +1416,7 @@
       <c r="D48" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E48" s="28" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="30" t="n"/>
@@ -1459,7 +1427,7 @@
         <v>97984</v>
       </c>
       <c r="D49" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="30" t="inlineStr"/>
     </row>
@@ -1472,7 +1440,7 @@
         <v>117576</v>
       </c>
       <c r="D50" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="30" t="inlineStr"/>
     </row>
@@ -1485,7 +1453,7 @@
         <v>141096</v>
       </c>
       <c r="D51" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="30" t="inlineStr"/>
     </row>
@@ -1498,7 +1466,7 @@
         <v>169312</v>
       </c>
       <c r="D52" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="30" t="inlineStr"/>
     </row>
@@ -1513,11 +1481,7 @@
       <c r="D53" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E53" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E53" s="28" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="30" t="n"/>
@@ -1528,7 +1492,7 @@
         <v>243816</v>
       </c>
       <c r="D54" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="30" t="inlineStr"/>
     </row>
@@ -1541,7 +1505,7 @@
         <v>292576</v>
       </c>
       <c r="D55" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="30" t="inlineStr"/>
     </row>
@@ -1554,7 +1518,7 @@
         <v>351096</v>
       </c>
       <c r="D56" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="30" t="inlineStr"/>
     </row>
@@ -1567,7 +1531,7 @@
         <v>421312</v>
       </c>
       <c r="D57" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="30" t="inlineStr"/>
     </row>
@@ -1582,11 +1546,7 @@
       <c r="D58" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E58" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="30" t="n"/>
@@ -1597,7 +1557,7 @@
         <v>606688</v>
       </c>
       <c r="D59" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="30" t="inlineStr"/>
     </row>
@@ -1610,7 +1570,7 @@
         <v>728032</v>
       </c>
       <c r="D60" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="30" t="inlineStr"/>
     </row>
@@ -1623,7 +1583,7 @@
         <v>873640</v>
       </c>
       <c r="D61" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="30" t="inlineStr"/>
     </row>
@@ -1636,7 +1596,7 @@
         <v>1048368</v>
       </c>
       <c r="D62" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="30" t="inlineStr"/>
     </row>
@@ -1651,11 +1611,7 @@
       <c r="D63" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E63" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E63" s="28" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="30" t="n"/>
@@ -1666,7 +1622,7 @@
         <v>1509648</v>
       </c>
       <c r="D64" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="30" t="inlineStr"/>
     </row>
@@ -1679,7 +1635,7 @@
         <v>1811584</v>
       </c>
       <c r="D65" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="30" t="inlineStr"/>
     </row>
@@ -1692,7 +1648,7 @@
         <v>2173896</v>
       </c>
       <c r="D66" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="30" t="inlineStr"/>
     </row>
@@ -1705,7 +1661,7 @@
         <v>2608680</v>
       </c>
       <c r="D67" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="30" t="inlineStr"/>
     </row>
@@ -1720,11 +1676,7 @@
       <c r="D68" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E68" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E68" s="28" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="30" t="n"/>
@@ -1735,7 +1687,7 @@
         <v>3756496</v>
       </c>
       <c r="D69" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="30" t="inlineStr"/>
     </row>
@@ -1748,7 +1700,7 @@
         <v>4507800</v>
       </c>
       <c r="D70" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="30" t="inlineStr"/>
     </row>
@@ -1761,7 +1713,7 @@
         <v>5409360</v>
       </c>
       <c r="D71" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="30" t="inlineStr"/>
     </row>
@@ -1774,7 +1726,7 @@
         <v>6491232</v>
       </c>
       <c r="D72" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="30" t="inlineStr"/>
     </row>
@@ -1789,11 +1741,7 @@
       <c r="D73" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E73" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E73" s="28" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="30" t="n"/>
@@ -1804,7 +1752,7 @@
         <v>9347376</v>
       </c>
       <c r="D74" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="30" t="inlineStr"/>
     </row>
@@ -1817,7 +1765,7 @@
         <v>11216848</v>
       </c>
       <c r="D75" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="30" t="inlineStr"/>
     </row>
@@ -1830,7 +1778,7 @@
         <v>13460216</v>
       </c>
       <c r="D76" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="30" t="inlineStr"/>
     </row>
@@ -1843,7 +1791,7 @@
         <v>16152264</v>
       </c>
       <c r="D77" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="30" t="inlineStr"/>
     </row>
@@ -1858,11 +1806,7 @@
       <c r="D78" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E78" s="28" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="30" t="n"/>
@@ -1873,7 +1817,7 @@
         <v>23259256</v>
       </c>
       <c r="D79" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79" s="30" t="inlineStr"/>
     </row>
@@ -1886,7 +1830,7 @@
         <v>27911112</v>
       </c>
       <c r="D80" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" s="30" t="inlineStr"/>
     </row>
@@ -1899,7 +1843,7 @@
         <v>33493336</v>
       </c>
       <c r="D81" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" s="30" t="inlineStr"/>
     </row>
@@ -1912,7 +1856,7 @@
         <v>40192000</v>
       </c>
       <c r="D82" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" s="30" t="inlineStr"/>
     </row>
@@ -1927,11 +1871,7 @@
       <c r="D83" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E83" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E83" s="28" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="30" t="n"/>
@@ -1942,7 +1882,7 @@
         <v>57876488</v>
       </c>
       <c r="D84" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84" s="30" t="inlineStr"/>
     </row>
@@ -1955,7 +1895,7 @@
         <v>69451784</v>
       </c>
       <c r="D85" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="30" t="inlineStr"/>
     </row>
@@ -1968,7 +1908,7 @@
         <v>83342144</v>
       </c>
       <c r="D86" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="30" t="inlineStr"/>
     </row>
@@ -1981,7 +1921,7 @@
         <v>100010576</v>
       </c>
       <c r="D87" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" s="30" t="inlineStr"/>
     </row>
@@ -1996,11 +1936,7 @@
       <c r="D88" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E88" s="28" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="30" t="n"/>
@@ -2011,7 +1947,7 @@
         <v>144015224</v>
       </c>
       <c r="D89" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="30" t="inlineStr"/>
     </row>
@@ -2024,7 +1960,7 @@
         <v>172818272</v>
       </c>
       <c r="D90" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90" s="30" t="inlineStr"/>
     </row>
@@ -2037,7 +1973,7 @@
         <v>207381928</v>
       </c>
       <c r="D91" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" s="30" t="inlineStr"/>
     </row>
@@ -2050,7 +1986,7 @@
         <v>248858312</v>
       </c>
       <c r="D92" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="30" t="inlineStr"/>
     </row>
@@ -2065,11 +2001,7 @@
       <c r="D93" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E93" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E93" s="28" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="30" t="n"/>
@@ -2080,7 +2012,7 @@
         <v>358355976</v>
       </c>
       <c r="D94" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="30" t="inlineStr"/>
     </row>
@@ -2093,7 +2025,7 @@
         <v>430027168</v>
       </c>
       <c r="D95" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="30" t="inlineStr"/>
     </row>
@@ -2106,7 +2038,7 @@
         <v>516032608</v>
       </c>
       <c r="D96" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="30" t="inlineStr"/>
     </row>
@@ -2119,7 +2051,7 @@
         <v>619239128</v>
       </c>
       <c r="D97" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="30" t="inlineStr"/>
     </row>
@@ -2134,11 +2066,7 @@
       <c r="D98" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E98" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E98" s="28" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="30" t="n"/>
@@ -2149,7 +2077,7 @@
         <v>891704344</v>
       </c>
       <c r="D99" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="30" t="inlineStr"/>
     </row>
@@ -2162,7 +2090,7 @@
         <v>1070045216</v>
       </c>
       <c r="D100" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" s="30" t="inlineStr"/>
     </row>
@@ -2175,7 +2103,7 @@
         <v>1284054256</v>
       </c>
       <c r="D101" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="30" t="inlineStr"/>
     </row>
@@ -2188,7 +2116,7 @@
         <v>1540865112</v>
       </c>
       <c r="D102" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="30" t="inlineStr"/>
     </row>
@@ -2203,11 +2131,7 @@
       <c r="D103" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E103" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E103" s="28" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="30" t="n"/>
@@ -2218,7 +2142,7 @@
         <v>2218845768</v>
       </c>
       <c r="D104" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" s="30" t="inlineStr"/>
     </row>
@@ -2231,7 +2155,7 @@
         <v>2662614920</v>
       </c>
       <c r="D105" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="30" t="inlineStr"/>
     </row>
@@ -2244,7 +2168,7 @@
         <v>3195137904</v>
       </c>
       <c r="D106" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="30" t="inlineStr"/>
     </row>
@@ -2257,7 +2181,7 @@
         <v>3834165480</v>
       </c>
       <c r="D107" s="27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" s="30" t="inlineStr"/>
     </row>
@@ -2272,20 +2196,16 @@
       <c r="D108" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="28" t="inlineStr">
-        <is>
-          <t>특성 포인트 +1</t>
-        </is>
-      </c>
+      <c r="E108" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -3989,6 +3909,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/User.xlsx
+++ b/GameDesign/Excel/User.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="AccountLevelTable" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="UserTraitTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="UserTraitLevelTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -209,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -315,6 +316,12 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -417,6 +424,31 @@
 </file>
 
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>캐릭터 레벨 (= TID)</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
@@ -2210,15 +2242,944 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="30" t="n"/>
+      <c r="B1" s="30" t="n"/>
+      <c r="C1" s="30" t="n"/>
+      <c r="D1" s="30" t="n"/>
+      <c r="E1" s="30" t="n"/>
+      <c r="F1" s="30" t="n"/>
+      <c r="G1" s="30" t="n"/>
+      <c r="H1" s="30" t="n"/>
+      <c r="I1" s="30" t="n"/>
+      <c r="J1" s="30" t="n"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="A2" s="31" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>특성 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>레벨당 포인트</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="F2" s="33" t="inlineStr">
+        <is>
+          <t>대상 산업</t>
+        </is>
+      </c>
+      <c r="G2" s="33" t="inlineStr">
+        <is>
+          <t>레벨당 효과(‰)</t>
+        </is>
+      </c>
+      <c r="H2" s="33" t="inlineStr">
+        <is>
+          <t>기본 레벨</t>
+        </is>
+      </c>
+      <c r="I2" s="33" t="inlineStr">
+        <is>
+          <t>최대 레벨</t>
+        </is>
+      </c>
+      <c r="J2" s="33" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17.25" customHeight="1">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.25" customHeight="1">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>eUserTraitEffect</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>eIndustryType</t>
+        </is>
+      </c>
+      <c r="G4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="34" t="n"/>
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="24" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="n"/>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+      <c r="E7" s="24" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
+      <c r="J7" s="34" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
+      <c r="J8" s="34" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>UserTraitTID</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>TraitPoint</t>
+        </is>
+      </c>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>EffectType</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>EffectValue</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>BaseLevel</t>
+        </is>
+      </c>
+      <c r="I9" s="36" t="inlineStr">
+        <is>
+          <t>MaxLevel</t>
+        </is>
+      </c>
+      <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="27" t="n">
+        <v>101</v>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>농사 개척</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" s="28" t="inlineStr">
+        <is>
+          <t>농사 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="27" t="n">
+        <v>102</v>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>낚시 개척</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="27" t="n">
+        <v>103</v>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>채굴 개척</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="27" t="n">
+        <v>104</v>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>벌목 개척</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="27" t="n">
+        <v>105</v>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>사냥 개척</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>IndustryUnlock</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="27" t="n">
+        <v>201</v>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>농사 속도</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="F15" s="28" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="28" t="inlineStr">
+        <is>
+          <t>농사 작업속도 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="n"/>
+      <c r="B16" s="27" t="n">
+        <v>202</v>
+      </c>
+      <c r="C16" s="28" t="inlineStr">
+        <is>
+          <t>낚시 속도</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="28" t="inlineStr">
+        <is>
+          <t>낚시 작업속도 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="F17" s="28" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="28" t="inlineStr">
+        <is>
+          <t>채굴 작업속도 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="n"/>
+      <c r="B18" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="28" t="inlineStr">
+        <is>
+          <t>벌목 작업속도 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>SpeedAdd</t>
+        </is>
+      </c>
+      <c r="F19" s="28" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" s="28" t="inlineStr">
+        <is>
+          <t>사냥 작업속도 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J20" s="28" t="inlineStr">
+        <is>
+          <t>전 산업 산출량 레벨당 +2% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F21" s="28" t="inlineStr">
+        <is>
+          <t>Farming</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
+          <t>Fishing</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="n"/>
+      <c r="B24" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>YieldAdd</t>
+        </is>
+      </c>
+      <c r="F25" s="28" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 레벨당 +5% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="31" customWidth="1" min="8" max="8"/>
   </cols>
@@ -2241,39 +3202,31 @@
       </c>
       <c r="B2" s="23" t="inlineStr">
         <is>
+          <t>레벨 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
           <t>특성 TID</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>특성 포인트</t>
+          <t>특성 레벨</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>효과</t>
+          <t>계정 레벨 조건</t>
         </is>
       </c>
       <c r="F2" s="33" t="inlineStr">
         <is>
-          <t>대상 산업</t>
-        </is>
-      </c>
-      <c r="G2" s="33" t="inlineStr">
-        <is>
-          <t>효과 값(‰)</t>
-        </is>
-      </c>
-      <c r="H2" s="33" t="inlineStr">
-        <is>
           <t>메모</t>
         </is>
       </c>
+      <c r="G2" s="37" t="n"/>
+      <c r="H2" s="37" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="31" t="inlineStr">
@@ -2306,16 +3259,8 @@
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="34" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="H3" s="34" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -2330,34 +3275,26 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>eUserTraitEffect</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="inlineStr">
-        <is>
-          <t>eIndustryType</t>
-        </is>
-      </c>
-      <c r="G4" s="34" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H4" s="34" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
+      <c r="G4" s="35" t="n"/>
+      <c r="H4" s="35" t="n"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="31" t="inlineStr">
@@ -2372,12 +3309,12 @@
       <c r="D5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="24" t="n"/>
+      <c r="E5" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" s="34" t="n"/>
-      <c r="G5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="34" t="n"/>
+      <c r="G5" s="35" t="n"/>
+      <c r="H5" s="35" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -2390,8 +3327,8 @@
       <c r="D6" s="24" t="n"/>
       <c r="E6" s="24" t="n"/>
       <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="35" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -2403,13 +3340,13 @@
       <c r="C7" s="24" t="n"/>
       <c r="D7" s="24" t="n"/>
       <c r="E7" s="24" t="n"/>
-      <c r="F7" s="34" t="n"/>
-      <c r="G7" s="34" t="n"/>
-      <c r="H7" s="34" t="inlineStr">
+      <c r="F7" s="34" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
+      <c r="G7" s="35" t="n"/>
+      <c r="H7" s="35" t="n"/>
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="35" t="inlineStr">
@@ -2417,1495 +3354,2907 @@
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>UnlockTable.UnlockTID</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>UserTraitTable.UserTraitTID</t>
+        </is>
+      </c>
       <c r="D8" s="34" t="n"/>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="n"/>
+      <c r="G8" s="35" t="n"/>
+      <c r="H8" s="35" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="n"/>
       <c r="B9" s="29" t="inlineStr">
         <is>
+          <t>UserTraitLevelTID</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
           <t>UserTraitTID</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>TraitPoint</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>EffectType</t>
+          <t>AccountLevel</t>
         </is>
       </c>
       <c r="F9" s="36" t="inlineStr">
         <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="G9" s="36" t="inlineStr">
-        <is>
-          <t>EffectValue</t>
-        </is>
-      </c>
-      <c r="H9" s="36" t="inlineStr">
-        <is>
           <t>Description</t>
         </is>
       </c>
+      <c r="G9" s="38" t="n"/>
+      <c r="H9" s="38" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="30" t="n"/>
       <c r="B10" s="27" t="n">
-        <v>2102</v>
-      </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>농사 Lv2</t>
-        </is>
+        <v>10102</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>101</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>농사 산업 레벨 2 해금</t>
-        </is>
-      </c>
+          <t>농사 개척 Lv2</t>
+        </is>
+      </c>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="28" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="30" t="n"/>
       <c r="B11" s="27" t="n">
-        <v>2103</v>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>농사 Lv3</t>
-        </is>
+        <v>10103</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>101</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="28" t="inlineStr">
-        <is>
-          <t>농사 산업 레벨 3 해금</t>
-        </is>
-      </c>
+          <t>농사 개척 Lv3</t>
+        </is>
+      </c>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="28" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="30" t="n"/>
       <c r="B12" s="27" t="n">
-        <v>2104</v>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t>농사 Lv4</t>
-        </is>
+        <v>10104</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>101</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G12" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="28" t="inlineStr">
-        <is>
-          <t>농사 산업 레벨 4 해금</t>
-        </is>
-      </c>
+          <t>농사 개척 Lv4</t>
+        </is>
+      </c>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="28" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="30" t="n"/>
       <c r="B13" s="27" t="n">
-        <v>2105</v>
-      </c>
-      <c r="C13" s="28" t="inlineStr">
-        <is>
-          <t>농사 Lv5</t>
-        </is>
+        <v>10105</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>101</v>
       </c>
       <c r="D13" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>50</v>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>농사 산업 레벨 5 해금</t>
-        </is>
-      </c>
+          <t>농사 개척 Lv5</t>
+        </is>
+      </c>
+      <c r="G13" s="27" t="n"/>
+      <c r="H13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="n"/>
       <c r="B14" s="27" t="n">
-        <v>2202</v>
-      </c>
-      <c r="C14" s="28" t="inlineStr">
-        <is>
-          <t>낚시 Lv2</t>
-        </is>
+        <v>10202</v>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>102</v>
       </c>
       <c r="D14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G14" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="28" t="inlineStr">
-        <is>
-          <t>낚시 산업 레벨 2 해금</t>
-        </is>
-      </c>
+          <t>낚시 개척 Lv2</t>
+        </is>
+      </c>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="28" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="30" t="n"/>
       <c r="B15" s="27" t="n">
-        <v>2203</v>
-      </c>
-      <c r="C15" s="28" t="inlineStr">
-        <is>
-          <t>낚시 Lv3</t>
-        </is>
+        <v>10203</v>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>102</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="28" t="inlineStr">
-        <is>
-          <t>낚시 산업 레벨 3 해금</t>
-        </is>
-      </c>
+          <t>낚시 개척 Lv3</t>
+        </is>
+      </c>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="28" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="30" t="n"/>
       <c r="B16" s="27" t="n">
-        <v>2204</v>
-      </c>
-      <c r="C16" s="28" t="inlineStr">
-        <is>
-          <t>낚시 Lv4</t>
-        </is>
+        <v>10204</v>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>102</v>
       </c>
       <c r="D16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="28" t="inlineStr">
-        <is>
-          <t>낚시 산업 레벨 4 해금</t>
-        </is>
-      </c>
+          <t>낚시 개척 Lv4</t>
+        </is>
+      </c>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="28" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="30" t="n"/>
       <c r="B17" s="27" t="n">
-        <v>2205</v>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
-        <is>
-          <t>낚시 Lv5</t>
-        </is>
+        <v>10205</v>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>102</v>
       </c>
       <c r="D17" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>50</v>
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="28" t="inlineStr">
-        <is>
-          <t>낚시 산업 레벨 5 해금</t>
-        </is>
-      </c>
+          <t>낚시 개척 Lv5</t>
+        </is>
+      </c>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="28" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="30" t="n"/>
       <c r="B18" s="27" t="n">
-        <v>2302</v>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>채굴 Lv2</t>
-        </is>
+        <v>10302</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>103</v>
       </c>
       <c r="D18" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F18" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="28" t="inlineStr">
-        <is>
-          <t>채굴 산업 레벨 2 해금</t>
-        </is>
-      </c>
+          <t>채굴 개척 Lv2</t>
+        </is>
+      </c>
+      <c r="G18" s="27" t="n"/>
+      <c r="H18" s="28" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="n"/>
       <c r="B19" s="27" t="n">
-        <v>2303</v>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>채굴 Lv3</t>
-        </is>
+        <v>10303</v>
+      </c>
+      <c r="C19" s="27" t="n">
+        <v>103</v>
       </c>
       <c r="D19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="28" t="inlineStr">
-        <is>
-          <t>채굴 산업 레벨 3 해금</t>
-        </is>
-      </c>
+          <t>채굴 개척 Lv3</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="n"/>
+      <c r="H19" s="28" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="30" t="n"/>
       <c r="B20" s="27" t="n">
-        <v>2304</v>
-      </c>
-      <c r="C20" s="28" t="inlineStr">
-        <is>
-          <t>채굴 Lv4</t>
-        </is>
+        <v>10304</v>
+      </c>
+      <c r="C20" s="27" t="n">
+        <v>103</v>
       </c>
       <c r="D20" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="28" t="inlineStr">
-        <is>
-          <t>채굴 산업 레벨 4 해금</t>
-        </is>
-      </c>
+          <t>채굴 개척 Lv4</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="28" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="30" t="n"/>
       <c r="B21" s="27" t="n">
-        <v>2305</v>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>채굴 Lv5</t>
-        </is>
+        <v>10305</v>
+      </c>
+      <c r="C21" s="27" t="n">
+        <v>103</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>50</v>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G21" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="28" t="inlineStr">
-        <is>
-          <t>채굴 산업 레벨 5 해금</t>
-        </is>
-      </c>
+          <t>채굴 개척 Lv5</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="28" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="30" t="n"/>
       <c r="B22" s="27" t="n">
-        <v>2402</v>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>벌목 Lv2</t>
-        </is>
+        <v>10402</v>
+      </c>
+      <c r="C22" s="27" t="n">
+        <v>104</v>
       </c>
       <c r="D22" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F22" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G22" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="28" t="inlineStr">
-        <is>
-          <t>벌목 산업 레벨 2 해금</t>
-        </is>
-      </c>
+          <t>벌목 개척 Lv2</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="n"/>
+      <c r="H22" s="28" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="30" t="n"/>
       <c r="B23" s="27" t="n">
-        <v>2403</v>
-      </c>
-      <c r="C23" s="28" t="inlineStr">
-        <is>
-          <t>벌목 Lv3</t>
-        </is>
+        <v>10403</v>
+      </c>
+      <c r="C23" s="27" t="n">
+        <v>104</v>
       </c>
       <c r="D23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G23" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="28" t="inlineStr">
-        <is>
-          <t>벌목 산업 레벨 3 해금</t>
-        </is>
-      </c>
+          <t>벌목 개척 Lv3</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="n"/>
+      <c r="H23" s="28" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="30" t="n"/>
       <c r="B24" s="27" t="n">
-        <v>2404</v>
-      </c>
-      <c r="C24" s="28" t="inlineStr">
-        <is>
-          <t>벌목 Lv4</t>
-        </is>
+        <v>10404</v>
+      </c>
+      <c r="C24" s="27" t="n">
+        <v>104</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F24" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G24" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="28" t="inlineStr">
-        <is>
-          <t>벌목 산업 레벨 4 해금</t>
-        </is>
-      </c>
+          <t>벌목 개척 Lv4</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="28" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="30" t="n"/>
       <c r="B25" s="27" t="n">
-        <v>2405</v>
-      </c>
-      <c r="C25" s="28" t="inlineStr">
-        <is>
-          <t>벌목 Lv5</t>
-        </is>
+        <v>10405</v>
+      </c>
+      <c r="C25" s="27" t="n">
+        <v>104</v>
       </c>
       <c r="D25" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>50</v>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G25" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>벌목 산업 레벨 5 해금</t>
-        </is>
-      </c>
+          <t>벌목 개척 Lv5</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="n"/>
+      <c r="H25" s="28" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="30" t="n"/>
       <c r="B26" s="27" t="n">
-        <v>2502</v>
-      </c>
-      <c r="C26" s="28" t="inlineStr">
-        <is>
-          <t>사냥 Lv2</t>
-        </is>
+        <v>10502</v>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>105</v>
       </c>
       <c r="D26" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G26" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="28" t="inlineStr">
-        <is>
-          <t>사냥 산업 레벨 2 해금</t>
-        </is>
-      </c>
+          <t>사냥 개척 Lv2</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="n"/>
+      <c r="H26" s="28" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="30" t="n"/>
       <c r="B27" s="27" t="n">
-        <v>2503</v>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>사냥 Lv3</t>
-        </is>
+        <v>10503</v>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>105</v>
       </c>
       <c r="D27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G27" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>사냥 산업 레벨 3 해금</t>
-        </is>
-      </c>
+          <t>사냥 개척 Lv3</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="n"/>
+      <c r="H27" s="28" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="30" t="n"/>
       <c r="B28" s="27" t="n">
-        <v>2504</v>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>사냥 Lv4</t>
-        </is>
+        <v>10504</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>105</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E28" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F28" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G28" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="28" t="inlineStr">
-        <is>
-          <t>사냥 산업 레벨 4 해금</t>
-        </is>
-      </c>
+          <t>사냥 개척 Lv4</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="n"/>
+      <c r="H28" s="28" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="30" t="n"/>
       <c r="B29" s="27" t="n">
-        <v>2505</v>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>사냥 Lv5</t>
-        </is>
+        <v>10505</v>
+      </c>
+      <c r="C29" s="27" t="n">
+        <v>105</v>
       </c>
       <c r="D29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E29" s="27" t="n">
+        <v>50</v>
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G29" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>사냥 산업 레벨 5 해금</t>
-        </is>
-      </c>
+          <t>사냥 개척 Lv5</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="n"/>
+      <c r="H29" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="30" t="n"/>
       <c r="B30" s="27" t="n">
-        <v>3101</v>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>농사 속도 10%</t>
-        </is>
+        <v>20101</v>
+      </c>
+      <c r="C30" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D30" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+      <c r="E30" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G30" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>농사 작업속도 +10% (누적 10%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv1</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="n"/>
+      <c r="H30" s="28" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="30" t="n"/>
       <c r="B31" s="27" t="n">
-        <v>3102</v>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>농사 속도 20%</t>
-        </is>
+        <v>20102</v>
+      </c>
+      <c r="C31" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D31" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G31" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>농사 작업속도 +10% (누적 20%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv2</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="n"/>
+      <c r="H31" s="28" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="30" t="n"/>
       <c r="B32" s="27" t="n">
-        <v>3103</v>
-      </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>농사 속도 30%</t>
-        </is>
+        <v>20103</v>
+      </c>
+      <c r="C32" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E32" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="F32" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G32" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H32" s="28" t="inlineStr">
-        <is>
-          <t>농사 작업속도 +10% (누적 30%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv3</t>
+        </is>
+      </c>
+      <c r="G32" s="27" t="n"/>
+      <c r="H32" s="28" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="30" t="n"/>
       <c r="B33" s="27" t="n">
-        <v>3104</v>
-      </c>
-      <c r="C33" s="28" t="inlineStr">
-        <is>
-          <t>농사 속도 40%</t>
-        </is>
+        <v>20104</v>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D33" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="28" t="inlineStr">
-        <is>
-          <t>농사 작업속도 +10% (누적 40%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv4</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="n"/>
+      <c r="H33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="30" t="n"/>
       <c r="B34" s="27" t="n">
-        <v>3105</v>
-      </c>
-      <c r="C34" s="28" t="inlineStr">
-        <is>
-          <t>농사 속도 50%</t>
-        </is>
+        <v>20105</v>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>Farming</t>
-        </is>
-      </c>
-      <c r="G34" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H34" s="28" t="inlineStr">
-        <is>
-          <t>농사 작업속도 +10% (누적 50%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv5</t>
+        </is>
+      </c>
+      <c r="G34" s="27" t="n"/>
+      <c r="H34" s="28" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="30" t="n"/>
       <c r="B35" s="27" t="n">
-        <v>3201</v>
-      </c>
-      <c r="C35" s="28" t="inlineStr">
-        <is>
-          <t>낚시 속도 10%</t>
-        </is>
+        <v>20106</v>
+      </c>
+      <c r="C35" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E35" s="27" t="n">
+        <v>25</v>
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G35" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H35" s="28" t="inlineStr">
-        <is>
-          <t>낚시 작업속도 +10% (누적 10%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv6</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="n"/>
+      <c r="H35" s="28" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="30" t="n"/>
       <c r="B36" s="27" t="n">
-        <v>3202</v>
-      </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>낚시 속도 20%</t>
-        </is>
+        <v>20107</v>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D36" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E36" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F36" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G36" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36" s="28" t="inlineStr">
-        <is>
-          <t>낚시 작업속도 +10% (누적 20%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv7</t>
+        </is>
+      </c>
+      <c r="G36" s="27" t="n"/>
+      <c r="H36" s="28" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="30" t="n"/>
       <c r="B37" s="27" t="n">
-        <v>3203</v>
-      </c>
-      <c r="C37" s="28" t="inlineStr">
-        <is>
-          <t>낚시 속도 30%</t>
-        </is>
+        <v>20108</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D37" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <v>35</v>
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G37" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H37" s="28" t="inlineStr">
-        <is>
-          <t>낚시 작업속도 +10% (누적 30%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv8</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="n"/>
+      <c r="H37" s="28" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="30" t="n"/>
       <c r="B38" s="27" t="n">
-        <v>3204</v>
-      </c>
-      <c r="C38" s="28" t="inlineStr">
-        <is>
-          <t>낚시 속도 40%</t>
-        </is>
+        <v>20109</v>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="E38" s="27" t="n">
+        <v>40</v>
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G38" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" s="28" t="inlineStr">
-        <is>
-          <t>낚시 작업속도 +10% (누적 40%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv9</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="n"/>
+      <c r="H38" s="28" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="30" t="n"/>
       <c r="B39" s="27" t="n">
-        <v>3205</v>
-      </c>
-      <c r="C39" s="28" t="inlineStr">
-        <is>
-          <t>낚시 속도 50%</t>
-        </is>
+        <v>20110</v>
+      </c>
+      <c r="C39" s="27" t="n">
+        <v>201</v>
       </c>
       <c r="D39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="E39" s="27" t="n">
+        <v>45</v>
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
-        </is>
-      </c>
-      <c r="G39" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H39" s="28" t="inlineStr">
-        <is>
-          <t>낚시 작업속도 +10% (누적 50%)</t>
-        </is>
-      </c>
+          <t>농사 속도 Lv10</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="n"/>
+      <c r="H39" s="28" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="30" t="n"/>
       <c r="B40" s="27" t="n">
-        <v>3301</v>
-      </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>채굴 속도 10%</t>
-        </is>
+        <v>20201</v>
+      </c>
+      <c r="C40" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D40" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E40" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+      <c r="E40" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G40" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H40" s="28" t="inlineStr">
-        <is>
-          <t>채굴 작업속도 +10% (누적 10%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv1</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="n"/>
+      <c r="H40" s="28" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="30" t="n"/>
       <c r="B41" s="27" t="n">
-        <v>3302</v>
-      </c>
-      <c r="C41" s="28" t="inlineStr">
-        <is>
-          <t>채굴 속도 20%</t>
-        </is>
+        <v>20202</v>
+      </c>
+      <c r="C41" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E41" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G41" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H41" s="28" t="inlineStr">
-        <is>
-          <t>채굴 작업속도 +10% (누적 20%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv2</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="n"/>
+      <c r="H41" s="28" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="30" t="n"/>
       <c r="B42" s="27" t="n">
-        <v>3303</v>
-      </c>
-      <c r="C42" s="28" t="inlineStr">
-        <is>
-          <t>채굴 속도 30%</t>
-        </is>
+        <v>20203</v>
+      </c>
+      <c r="C42" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D42" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E42" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="F42" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G42" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H42" s="28" t="inlineStr">
-        <is>
-          <t>채굴 작업속도 +10% (누적 30%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv3</t>
+        </is>
+      </c>
+      <c r="G42" s="27" t="n"/>
+      <c r="H42" s="28" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="30" t="n"/>
       <c r="B43" s="27" t="n">
-        <v>3304</v>
-      </c>
-      <c r="C43" s="28" t="inlineStr">
-        <is>
-          <t>채굴 속도 40%</t>
-        </is>
+        <v>20204</v>
+      </c>
+      <c r="C43" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E43" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G43" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H43" s="28" t="inlineStr">
-        <is>
-          <t>채굴 작업속도 +10% (누적 40%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv4</t>
+        </is>
+      </c>
+      <c r="G43" s="27" t="n"/>
+      <c r="H43" s="28" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="30" t="n"/>
       <c r="B44" s="27" t="n">
-        <v>3305</v>
-      </c>
-      <c r="C44" s="28" t="inlineStr">
-        <is>
-          <t>채굴 속도 50%</t>
-        </is>
+        <v>20205</v>
+      </c>
+      <c r="C44" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D44" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E44" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>Mining</t>
-        </is>
-      </c>
-      <c r="G44" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H44" s="28" t="inlineStr">
-        <is>
-          <t>채굴 작업속도 +10% (누적 50%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv5</t>
+        </is>
+      </c>
+      <c r="G44" s="27" t="n"/>
+      <c r="H44" s="28" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="30" t="n"/>
       <c r="B45" s="27" t="n">
-        <v>3401</v>
-      </c>
-      <c r="C45" s="28" t="inlineStr">
-        <is>
-          <t>벌목 속도 10%</t>
-        </is>
+        <v>20206</v>
+      </c>
+      <c r="C45" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E45" s="27" t="n">
+        <v>25</v>
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G45" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H45" s="28" t="inlineStr">
-        <is>
-          <t>벌목 작업속도 +10% (누적 10%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv6</t>
+        </is>
+      </c>
+      <c r="G45" s="27" t="n"/>
+      <c r="H45" s="28" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="30" t="n"/>
       <c r="B46" s="27" t="n">
-        <v>3402</v>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>벌목 속도 20%</t>
-        </is>
+        <v>20207</v>
+      </c>
+      <c r="C46" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D46" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E46" s="27" t="n">
+        <v>30</v>
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G46" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H46" s="28" t="inlineStr">
-        <is>
-          <t>벌목 작업속도 +10% (누적 20%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv7</t>
+        </is>
+      </c>
+      <c r="G46" s="27" t="n"/>
+      <c r="H46" s="28" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="30" t="n"/>
       <c r="B47" s="27" t="n">
-        <v>3403</v>
-      </c>
-      <c r="C47" s="28" t="inlineStr">
-        <is>
-          <t>벌목 속도 30%</t>
-        </is>
+        <v>20208</v>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D47" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E47" s="27" t="n">
+        <v>35</v>
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G47" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H47" s="28" t="inlineStr">
-        <is>
-          <t>벌목 작업속도 +10% (누적 30%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv8</t>
+        </is>
+      </c>
+      <c r="G47" s="27" t="n"/>
+      <c r="H47" s="28" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="30" t="n"/>
       <c r="B48" s="27" t="n">
-        <v>3404</v>
-      </c>
-      <c r="C48" s="28" t="inlineStr">
-        <is>
-          <t>벌목 속도 40%</t>
-        </is>
+        <v>20209</v>
+      </c>
+      <c r="C48" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D48" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="E48" s="27" t="n">
+        <v>40</v>
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G48" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H48" s="28" t="inlineStr">
-        <is>
-          <t>벌목 작업속도 +10% (누적 40%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv9</t>
+        </is>
+      </c>
+      <c r="G48" s="27" t="n"/>
+      <c r="H48" s="28" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="30" t="n"/>
       <c r="B49" s="27" t="n">
-        <v>3405</v>
-      </c>
-      <c r="C49" s="28" t="inlineStr">
-        <is>
-          <t>벌목 속도 50%</t>
-        </is>
+        <v>20210</v>
+      </c>
+      <c r="C49" s="27" t="n">
+        <v>202</v>
       </c>
       <c r="D49" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="E49" s="27" t="n">
+        <v>45</v>
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>Logging</t>
-        </is>
-      </c>
-      <c r="G49" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="28" t="inlineStr">
-        <is>
-          <t>벌목 작업속도 +10% (누적 50%)</t>
-        </is>
-      </c>
+          <t>낚시 속도 Lv10</t>
+        </is>
+      </c>
+      <c r="G49" s="27" t="n"/>
+      <c r="H49" s="28" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="30" t="n"/>
       <c r="B50" s="27" t="n">
-        <v>3501</v>
-      </c>
-      <c r="C50" s="28" t="inlineStr">
-        <is>
-          <t>사냥 속도 10%</t>
-        </is>
+        <v>20301</v>
+      </c>
+      <c r="C50" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="D50" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="E50" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+      <c r="E50" s="27" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G50" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H50" s="28" t="inlineStr">
-        <is>
-          <t>사냥 작업속도 +10% (누적 10%)</t>
-        </is>
-      </c>
+          <t>채굴 속도 Lv1</t>
+        </is>
+      </c>
+      <c r="G50" s="27" t="n"/>
+      <c r="H50" s="28" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="30" t="n"/>
       <c r="B51" s="27" t="n">
-        <v>3502</v>
-      </c>
-      <c r="C51" s="28" t="inlineStr">
-        <is>
-          <t>사냥 속도 20%</t>
-        </is>
+        <v>20302</v>
+      </c>
+      <c r="C51" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="D51" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>5</v>
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G51" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H51" s="28" t="inlineStr">
-        <is>
-          <t>사냥 작업속도 +10% (누적 20%)</t>
-        </is>
-      </c>
+          <t>채굴 속도 Lv2</t>
+        </is>
+      </c>
+      <c r="G51" s="27" t="n"/>
+      <c r="H51" s="28" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="30" t="n"/>
       <c r="B52" s="27" t="n">
-        <v>3503</v>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>사냥 속도 30%</t>
-        </is>
+        <v>20303</v>
+      </c>
+      <c r="C52" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="D52" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E52" s="27" t="n">
+        <v>10</v>
       </c>
       <c r="F52" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G52" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H52" s="28" t="inlineStr">
-        <is>
-          <t>사냥 작업속도 +10% (누적 30%)</t>
-        </is>
-      </c>
+          <t>채굴 속도 Lv3</t>
+        </is>
+      </c>
+      <c r="G52" s="27" t="n"/>
+      <c r="H52" s="28" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="30" t="n"/>
       <c r="B53" s="27" t="n">
-        <v>3504</v>
-      </c>
-      <c r="C53" s="28" t="inlineStr">
-        <is>
-          <t>사냥 속도 40%</t>
-        </is>
+        <v>20304</v>
+      </c>
+      <c r="C53" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="D53" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="E53" s="27" t="n">
+        <v>15</v>
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G53" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H53" s="28" t="inlineStr">
-        <is>
-          <t>사냥 작업속도 +10% (누적 40%)</t>
-        </is>
-      </c>
+          <t>채굴 속도 Lv4</t>
+        </is>
+      </c>
+      <c r="G53" s="27" t="n"/>
+      <c r="H53" s="28" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="30" t="n"/>
       <c r="B54" s="27" t="n">
-        <v>3505</v>
-      </c>
-      <c r="C54" s="28" t="inlineStr">
-        <is>
-          <t>사냥 속도 50%</t>
-        </is>
+        <v>20305</v>
+      </c>
+      <c r="C54" s="27" t="n">
+        <v>203</v>
       </c>
       <c r="D54" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="28" t="inlineStr">
-        <is>
-          <t>SpeedAdd</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E54" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="F54" s="28" t="inlineStr">
         <is>
-          <t>Hunting</t>
-        </is>
-      </c>
-      <c r="G54" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="H54" s="28" t="inlineStr">
-        <is>
-          <t>사냥 작업속도 +10% (누적 50%)</t>
-        </is>
-      </c>
+          <t>채굴 속도 Lv5</t>
+        </is>
+      </c>
+      <c r="G54" s="27" t="n"/>
+      <c r="H54" s="28" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="30" t="n"/>
+      <c r="B55" s="27" t="n">
+        <v>20306</v>
+      </c>
+      <c r="C55" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="D55" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도 Lv6</t>
+        </is>
+      </c>
+      <c r="G55" s="30" t="n"/>
+      <c r="H55" s="30" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="n"/>
+      <c r="B56" s="27" t="n">
+        <v>20307</v>
+      </c>
+      <c r="C56" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="D56" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도 Lv7</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="n"/>
+      <c r="H56" s="30" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="30" t="n"/>
+      <c r="B57" s="27" t="n">
+        <v>20308</v>
+      </c>
+      <c r="C57" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="D57" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도 Lv8</t>
+        </is>
+      </c>
+      <c r="G57" s="30" t="n"/>
+      <c r="H57" s="30" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="30" t="n"/>
+      <c r="B58" s="27" t="n">
+        <v>20309</v>
+      </c>
+      <c r="C58" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="D58" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E58" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F58" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도 Lv9</t>
+        </is>
+      </c>
+      <c r="G58" s="30" t="n"/>
+      <c r="H58" s="30" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="n"/>
+      <c r="B59" s="27" t="n">
+        <v>20310</v>
+      </c>
+      <c r="C59" s="27" t="n">
+        <v>203</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>채굴 속도 Lv10</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="n"/>
+      <c r="H59" s="30" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="n"/>
+      <c r="B60" s="27" t="n">
+        <v>20401</v>
+      </c>
+      <c r="C60" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D60" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv1</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="n"/>
+      <c r="H60" s="30" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="n"/>
+      <c r="B61" s="27" t="n">
+        <v>20402</v>
+      </c>
+      <c r="C61" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D61" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv2</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="n"/>
+      <c r="H61" s="30" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="n"/>
+      <c r="B62" s="27" t="n">
+        <v>20403</v>
+      </c>
+      <c r="C62" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D62" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv3</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="n"/>
+      <c r="H62" s="30" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="n"/>
+      <c r="B63" s="27" t="n">
+        <v>20404</v>
+      </c>
+      <c r="C63" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D63" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv4</t>
+        </is>
+      </c>
+      <c r="G63" s="30" t="n"/>
+      <c r="H63" s="30" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="n"/>
+      <c r="B64" s="27" t="n">
+        <v>20405</v>
+      </c>
+      <c r="C64" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv5</t>
+        </is>
+      </c>
+      <c r="G64" s="30" t="n"/>
+      <c r="H64" s="30" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="n"/>
+      <c r="B65" s="27" t="n">
+        <v>20406</v>
+      </c>
+      <c r="C65" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D65" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv6</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="n"/>
+      <c r="H65" s="30" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="n"/>
+      <c r="B66" s="27" t="n">
+        <v>20407</v>
+      </c>
+      <c r="C66" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D66" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E66" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F66" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv7</t>
+        </is>
+      </c>
+      <c r="G66" s="30" t="n"/>
+      <c r="H66" s="30" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="n"/>
+      <c r="B67" s="27" t="n">
+        <v>20408</v>
+      </c>
+      <c r="C67" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D67" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E67" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv8</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="30" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="n"/>
+      <c r="B68" s="27" t="n">
+        <v>20409</v>
+      </c>
+      <c r="C68" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D68" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E68" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F68" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv9</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="n"/>
+      <c r="H68" s="30" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="n"/>
+      <c r="B69" s="27" t="n">
+        <v>20410</v>
+      </c>
+      <c r="C69" s="27" t="n">
+        <v>204</v>
+      </c>
+      <c r="D69" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>벌목 속도 Lv10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="n"/>
+      <c r="H69" s="30" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="n"/>
+      <c r="B70" s="27" t="n">
+        <v>20501</v>
+      </c>
+      <c r="C70" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D70" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv1</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="n"/>
+      <c r="H70" s="30" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="n"/>
+      <c r="B71" s="27" t="n">
+        <v>20502</v>
+      </c>
+      <c r="C71" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D71" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F71" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv2</t>
+        </is>
+      </c>
+      <c r="G71" s="30" t="n"/>
+      <c r="H71" s="30" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="n"/>
+      <c r="B72" s="27" t="n">
+        <v>20503</v>
+      </c>
+      <c r="C72" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D72" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv3</t>
+        </is>
+      </c>
+      <c r="G72" s="30" t="n"/>
+      <c r="H72" s="30" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="n"/>
+      <c r="B73" s="27" t="n">
+        <v>20504</v>
+      </c>
+      <c r="C73" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D73" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F73" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv4</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="n"/>
+      <c r="H73" s="30" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="n"/>
+      <c r="B74" s="27" t="n">
+        <v>20505</v>
+      </c>
+      <c r="C74" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D74" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F74" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv5</t>
+        </is>
+      </c>
+      <c r="G74" s="30" t="n"/>
+      <c r="H74" s="30" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="n"/>
+      <c r="B75" s="27" t="n">
+        <v>20506</v>
+      </c>
+      <c r="C75" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D75" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv6</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="n"/>
+      <c r="H75" s="30" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="n"/>
+      <c r="B76" s="27" t="n">
+        <v>20507</v>
+      </c>
+      <c r="C76" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D76" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F76" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv7</t>
+        </is>
+      </c>
+      <c r="G76" s="30" t="n"/>
+      <c r="H76" s="30" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="n"/>
+      <c r="B77" s="27" t="n">
+        <v>20508</v>
+      </c>
+      <c r="C77" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D77" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E77" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F77" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv8</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="n"/>
+      <c r="H77" s="30" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="30" t="n"/>
+      <c r="B78" s="27" t="n">
+        <v>20509</v>
+      </c>
+      <c r="C78" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D78" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E78" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F78" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv9</t>
+        </is>
+      </c>
+      <c r="G78" s="30" t="n"/>
+      <c r="H78" s="30" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="30" t="n"/>
+      <c r="B79" s="27" t="n">
+        <v>20510</v>
+      </c>
+      <c r="C79" s="27" t="n">
+        <v>205</v>
+      </c>
+      <c r="D79" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F79" s="28" t="inlineStr">
+        <is>
+          <t>사냥 속도 Lv10</t>
+        </is>
+      </c>
+      <c r="G79" s="30" t="n"/>
+      <c r="H79" s="30" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="30" t="n"/>
+      <c r="B80" s="27" t="n">
+        <v>30001</v>
+      </c>
+      <c r="C80" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D80" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G80" s="30" t="n"/>
+      <c r="H80" s="30" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="30" t="n"/>
+      <c r="B81" s="27" t="n">
+        <v>30002</v>
+      </c>
+      <c r="C81" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D81" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G81" s="30" t="n"/>
+      <c r="H81" s="30" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="n"/>
+      <c r="B82" s="27" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C82" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D82" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G82" s="30" t="n"/>
+      <c r="H82" s="30" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="n"/>
+      <c r="B83" s="27" t="n">
+        <v>30004</v>
+      </c>
+      <c r="C83" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D83" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F83" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G83" s="30" t="n"/>
+      <c r="H83" s="30" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="n"/>
+      <c r="B84" s="27" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C84" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D84" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E84" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F84" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G84" s="30" t="n"/>
+      <c r="H84" s="30" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="30" t="n"/>
+      <c r="B85" s="27" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C85" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D85" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E85" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F85" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G85" s="30" t="n"/>
+      <c r="H85" s="30" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="30" t="n"/>
+      <c r="B86" s="27" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C86" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D86" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E86" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F86" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G86" s="30" t="n"/>
+      <c r="H86" s="30" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="30" t="n"/>
+      <c r="B87" s="27" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C87" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D87" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E87" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F87" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G87" s="30" t="n"/>
+      <c r="H87" s="30" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="30" t="n"/>
+      <c r="B88" s="27" t="n">
+        <v>30009</v>
+      </c>
+      <c r="C88" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D88" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F88" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G88" s="30" t="n"/>
+      <c r="H88" s="30" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="30" t="n"/>
+      <c r="B89" s="27" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C89" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="D89" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F89" s="28" t="inlineStr">
+        <is>
+          <t>공통 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G89" s="30" t="n"/>
+      <c r="H89" s="30" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="30" t="n"/>
+      <c r="B90" s="27" t="n">
+        <v>30101</v>
+      </c>
+      <c r="C90" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D90" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G90" s="30" t="n"/>
+      <c r="H90" s="30" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="30" t="n"/>
+      <c r="B91" s="27" t="n">
+        <v>30102</v>
+      </c>
+      <c r="C91" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D91" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G91" s="30" t="n"/>
+      <c r="H91" s="30" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="30" t="n"/>
+      <c r="B92" s="27" t="n">
+        <v>30103</v>
+      </c>
+      <c r="C92" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D92" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G92" s="30" t="n"/>
+      <c r="H92" s="30" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="30" t="n"/>
+      <c r="B93" s="27" t="n">
+        <v>30104</v>
+      </c>
+      <c r="C93" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D93" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F93" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G93" s="30" t="n"/>
+      <c r="H93" s="30" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="30" t="n"/>
+      <c r="B94" s="27" t="n">
+        <v>30105</v>
+      </c>
+      <c r="C94" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D94" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E94" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F94" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G94" s="30" t="n"/>
+      <c r="H94" s="30" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="30" t="n"/>
+      <c r="B95" s="27" t="n">
+        <v>30106</v>
+      </c>
+      <c r="C95" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D95" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E95" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F95" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G95" s="30" t="n"/>
+      <c r="H95" s="30" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="30" t="n"/>
+      <c r="B96" s="27" t="n">
+        <v>30107</v>
+      </c>
+      <c r="C96" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D96" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E96" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F96" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G96" s="30" t="n"/>
+      <c r="H96" s="30" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="30" t="n"/>
+      <c r="B97" s="27" t="n">
+        <v>30108</v>
+      </c>
+      <c r="C97" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D97" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E97" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F97" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G97" s="30" t="n"/>
+      <c r="H97" s="30" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="30" t="n"/>
+      <c r="B98" s="27" t="n">
+        <v>30109</v>
+      </c>
+      <c r="C98" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D98" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E98" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F98" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G98" s="30" t="n"/>
+      <c r="H98" s="30" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="30" t="n"/>
+      <c r="B99" s="27" t="n">
+        <v>30110</v>
+      </c>
+      <c r="C99" s="27" t="n">
+        <v>301</v>
+      </c>
+      <c r="D99" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F99" s="28" t="inlineStr">
+        <is>
+          <t>농사 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G99" s="30" t="n"/>
+      <c r="H99" s="30" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="30" t="n"/>
+      <c r="B100" s="27" t="n">
+        <v>30201</v>
+      </c>
+      <c r="C100" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D100" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G100" s="30" t="n"/>
+      <c r="H100" s="30" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="30" t="n"/>
+      <c r="B101" s="27" t="n">
+        <v>30202</v>
+      </c>
+      <c r="C101" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D101" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F101" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G101" s="30" t="n"/>
+      <c r="H101" s="30" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="30" t="n"/>
+      <c r="B102" s="27" t="n">
+        <v>30203</v>
+      </c>
+      <c r="C102" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D102" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F102" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G102" s="30" t="n"/>
+      <c r="H102" s="30" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="30" t="n"/>
+      <c r="B103" s="27" t="n">
+        <v>30204</v>
+      </c>
+      <c r="C103" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D103" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F103" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G103" s="30" t="n"/>
+      <c r="H103" s="30" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="30" t="n"/>
+      <c r="B104" s="27" t="n">
+        <v>30205</v>
+      </c>
+      <c r="C104" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D104" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F104" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G104" s="30" t="n"/>
+      <c r="H104" s="30" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="30" t="n"/>
+      <c r="B105" s="27" t="n">
+        <v>30206</v>
+      </c>
+      <c r="C105" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D105" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F105" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G105" s="30" t="n"/>
+      <c r="H105" s="30" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="30" t="n"/>
+      <c r="B106" s="27" t="n">
+        <v>30207</v>
+      </c>
+      <c r="C106" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D106" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E106" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F106" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G106" s="30" t="n"/>
+      <c r="H106" s="30" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="30" t="n"/>
+      <c r="B107" s="27" t="n">
+        <v>30208</v>
+      </c>
+      <c r="C107" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D107" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E107" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F107" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G107" s="30" t="n"/>
+      <c r="H107" s="30" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="30" t="n"/>
+      <c r="B108" s="27" t="n">
+        <v>30209</v>
+      </c>
+      <c r="C108" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D108" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E108" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F108" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G108" s="30" t="n"/>
+      <c r="H108" s="30" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="30" t="n"/>
+      <c r="B109" s="27" t="n">
+        <v>30210</v>
+      </c>
+      <c r="C109" s="27" t="n">
+        <v>302</v>
+      </c>
+      <c r="D109" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F109" s="28" t="inlineStr">
+        <is>
+          <t>낚시 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G109" s="30" t="n"/>
+      <c r="H109" s="30" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="30" t="n"/>
+      <c r="B110" s="27" t="n">
+        <v>30301</v>
+      </c>
+      <c r="C110" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D110" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G110" s="30" t="n"/>
+      <c r="H110" s="30" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="30" t="n"/>
+      <c r="B111" s="27" t="n">
+        <v>30302</v>
+      </c>
+      <c r="C111" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D111" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G111" s="30" t="n"/>
+      <c r="H111" s="30" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="30" t="n"/>
+      <c r="B112" s="27" t="n">
+        <v>30303</v>
+      </c>
+      <c r="C112" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D112" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F112" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G112" s="30" t="n"/>
+      <c r="H112" s="30" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="30" t="n"/>
+      <c r="B113" s="27" t="n">
+        <v>30304</v>
+      </c>
+      <c r="C113" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D113" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F113" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G113" s="30" t="n"/>
+      <c r="H113" s="30" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="30" t="n"/>
+      <c r="B114" s="27" t="n">
+        <v>30305</v>
+      </c>
+      <c r="C114" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D114" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F114" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G114" s="30" t="n"/>
+      <c r="H114" s="30" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="30" t="n"/>
+      <c r="B115" s="27" t="n">
+        <v>30306</v>
+      </c>
+      <c r="C115" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D115" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F115" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G115" s="30" t="n"/>
+      <c r="H115" s="30" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="30" t="n"/>
+      <c r="B116" s="27" t="n">
+        <v>30307</v>
+      </c>
+      <c r="C116" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D116" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F116" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G116" s="30" t="n"/>
+      <c r="H116" s="30" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="n"/>
+      <c r="B117" s="27" t="n">
+        <v>30308</v>
+      </c>
+      <c r="C117" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D117" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E117" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F117" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G117" s="30" t="n"/>
+      <c r="H117" s="30" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="30" t="n"/>
+      <c r="B118" s="27" t="n">
+        <v>30309</v>
+      </c>
+      <c r="C118" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D118" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E118" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F118" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G118" s="30" t="n"/>
+      <c r="H118" s="30" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="30" t="n"/>
+      <c r="B119" s="27" t="n">
+        <v>30310</v>
+      </c>
+      <c r="C119" s="27" t="n">
+        <v>303</v>
+      </c>
+      <c r="D119" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F119" s="28" t="inlineStr">
+        <is>
+          <t>채굴 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G119" s="30" t="n"/>
+      <c r="H119" s="30" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="30" t="n"/>
+      <c r="B120" s="27" t="n">
+        <v>30401</v>
+      </c>
+      <c r="C120" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D120" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G120" s="30" t="n"/>
+      <c r="H120" s="30" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="30" t="n"/>
+      <c r="B121" s="27" t="n">
+        <v>30402</v>
+      </c>
+      <c r="C121" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D121" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G121" s="30" t="n"/>
+      <c r="H121" s="30" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="30" t="n"/>
+      <c r="B122" s="27" t="n">
+        <v>30403</v>
+      </c>
+      <c r="C122" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D122" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F122" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G122" s="30" t="n"/>
+      <c r="H122" s="30" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="30" t="n"/>
+      <c r="B123" s="27" t="n">
+        <v>30404</v>
+      </c>
+      <c r="C123" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D123" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E123" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F123" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G123" s="30" t="n"/>
+      <c r="H123" s="30" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="30" t="n"/>
+      <c r="B124" s="27" t="n">
+        <v>30405</v>
+      </c>
+      <c r="C124" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D124" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F124" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G124" s="30" t="n"/>
+      <c r="H124" s="30" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="30" t="n"/>
+      <c r="B125" s="27" t="n">
+        <v>30406</v>
+      </c>
+      <c r="C125" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D125" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F125" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G125" s="30" t="n"/>
+      <c r="H125" s="30" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="30" t="n"/>
+      <c r="B126" s="27" t="n">
+        <v>30407</v>
+      </c>
+      <c r="C126" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D126" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E126" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F126" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G126" s="30" t="n"/>
+      <c r="H126" s="30" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="30" t="n"/>
+      <c r="B127" s="27" t="n">
+        <v>30408</v>
+      </c>
+      <c r="C127" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D127" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E127" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F127" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G127" s="30" t="n"/>
+      <c r="H127" s="30" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="30" t="n"/>
+      <c r="B128" s="27" t="n">
+        <v>30409</v>
+      </c>
+      <c r="C128" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D128" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E128" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F128" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G128" s="30" t="n"/>
+      <c r="H128" s="30" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="n"/>
+      <c r="B129" s="27" t="n">
+        <v>30410</v>
+      </c>
+      <c r="C129" s="27" t="n">
+        <v>304</v>
+      </c>
+      <c r="D129" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E129" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F129" s="28" t="inlineStr">
+        <is>
+          <t>벌목 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G129" s="30" t="n"/>
+      <c r="H129" s="30" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="30" t="n"/>
+      <c r="B130" s="27" t="n">
+        <v>30501</v>
+      </c>
+      <c r="C130" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D130" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv1</t>
+        </is>
+      </c>
+      <c r="G130" s="30" t="n"/>
+      <c r="H130" s="30" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="30" t="n"/>
+      <c r="B131" s="27" t="n">
+        <v>30502</v>
+      </c>
+      <c r="C131" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D131" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv2</t>
+        </is>
+      </c>
+      <c r="G131" s="30" t="n"/>
+      <c r="H131" s="30" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="30" t="n"/>
+      <c r="B132" s="27" t="n">
+        <v>30503</v>
+      </c>
+      <c r="C132" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D132" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F132" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv3</t>
+        </is>
+      </c>
+      <c r="G132" s="30" t="n"/>
+      <c r="H132" s="30" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="n"/>
+      <c r="B133" s="27" t="n">
+        <v>30504</v>
+      </c>
+      <c r="C133" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D133" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E133" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="F133" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv4</t>
+        </is>
+      </c>
+      <c r="G133" s="30" t="n"/>
+      <c r="H133" s="30" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="n"/>
+      <c r="B134" s="27" t="n">
+        <v>30505</v>
+      </c>
+      <c r="C134" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D134" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F134" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv5</t>
+        </is>
+      </c>
+      <c r="G134" s="30" t="n"/>
+      <c r="H134" s="30" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="30" t="n"/>
+      <c r="B135" s="27" t="n">
+        <v>30506</v>
+      </c>
+      <c r="C135" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D135" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E135" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F135" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv6</t>
+        </is>
+      </c>
+      <c r="G135" s="30" t="n"/>
+      <c r="H135" s="30" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="30" t="n"/>
+      <c r="B136" s="27" t="n">
+        <v>30507</v>
+      </c>
+      <c r="C136" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D136" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E136" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F136" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv7</t>
+        </is>
+      </c>
+      <c r="G136" s="30" t="n"/>
+      <c r="H136" s="30" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="30" t="n"/>
+      <c r="B137" s="27" t="n">
+        <v>30508</v>
+      </c>
+      <c r="C137" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D137" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E137" s="27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F137" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv8</t>
+        </is>
+      </c>
+      <c r="G137" s="30" t="n"/>
+      <c r="H137" s="30" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="30" t="n"/>
+      <c r="B138" s="27" t="n">
+        <v>30509</v>
+      </c>
+      <c r="C138" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D138" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E138" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="F138" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv9</t>
+        </is>
+      </c>
+      <c r="G138" s="30" t="n"/>
+      <c r="H138" s="30" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="30" t="n"/>
+      <c r="B139" s="27" t="n">
+        <v>30510</v>
+      </c>
+      <c r="C139" s="27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D139" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E139" s="27" t="n">
+        <v>45</v>
+      </c>
+      <c r="F139" s="28" t="inlineStr">
+        <is>
+          <t>사냥 산출량 Lv10</t>
+        </is>
+      </c>
+      <c r="G139" s="30" t="n"/>
+      <c r="H139" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GameDesign/Excel/User.xlsx
+++ b/GameDesign/Excel/User.xlsx
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>낚시 개척</t>
+          <t>발굴 개척</t>
         </is>
       </c>
       <c r="D11" s="27" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G11" s="27" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="J11" s="28" t="inlineStr">
         <is>
-          <t>낚시 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
+          <t>발굴 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도</t>
+          <t>발굴 속도</t>
         </is>
       </c>
       <c r="D16" s="27" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G16" s="27" t="n">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="J16" s="28" t="inlineStr">
         <is>
-          <t>낚시 작업속도 레벨당 +5% (테스트값)</t>
+          <t>발굴 작업속도 레벨당 +5% (테스트값)</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량</t>
+          <t>발굴 산출량</t>
         </is>
       </c>
       <c r="D22" s="27" t="n">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F22" s="28" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Excavation</t>
         </is>
       </c>
       <c r="G22" s="27" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="J22" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 레벨당 +5% (테스트값)</t>
+          <t>발굴 산출량 레벨당 +5% (테스트값)</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>낚시 개척 Lv2</t>
+          <t>발굴 개척 Lv2</t>
         </is>
       </c>
       <c r="G14" s="27" t="n"/>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>낚시 개척 Lv3</t>
+          <t>발굴 개척 Lv3</t>
         </is>
       </c>
       <c r="G15" s="27" t="n"/>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F16" s="28" t="inlineStr">
         <is>
-          <t>낚시 개척 Lv4</t>
+          <t>발굴 개척 Lv4</t>
         </is>
       </c>
       <c r="G16" s="27" t="n"/>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>낚시 개척 Lv5</t>
+          <t>발굴 개척 Lv5</t>
         </is>
       </c>
       <c r="G17" s="27" t="n"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="F40" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv1</t>
+          <t>발굴 속도 Lv1</t>
         </is>
       </c>
       <c r="G40" s="27" t="n"/>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv2</t>
+          <t>발굴 속도 Lv2</t>
         </is>
       </c>
       <c r="G41" s="27" t="n"/>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="F42" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv3</t>
+          <t>발굴 속도 Lv3</t>
         </is>
       </c>
       <c r="G42" s="27" t="n"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv4</t>
+          <t>발굴 속도 Lv4</t>
         </is>
       </c>
       <c r="G43" s="27" t="n"/>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="F44" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv5</t>
+          <t>발굴 속도 Lv5</t>
         </is>
       </c>
       <c r="G44" s="27" t="n"/>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv6</t>
+          <t>발굴 속도 Lv6</t>
         </is>
       </c>
       <c r="G45" s="27" t="n"/>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv7</t>
+          <t>발굴 속도 Lv7</t>
         </is>
       </c>
       <c r="G46" s="27" t="n"/>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv8</t>
+          <t>발굴 속도 Lv8</t>
         </is>
       </c>
       <c r="G47" s="27" t="n"/>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv9</t>
+          <t>발굴 속도 Lv9</t>
         </is>
       </c>
       <c r="G48" s="27" t="n"/>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>낚시 속도 Lv10</t>
+          <t>발굴 속도 Lv10</t>
         </is>
       </c>
       <c r="G49" s="27" t="n"/>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="F100" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv1</t>
+          <t>발굴 산출량 Lv1</t>
         </is>
       </c>
       <c r="G100" s="30" t="n"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="F101" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv2</t>
+          <t>발굴 산출량 Lv2</t>
         </is>
       </c>
       <c r="G101" s="30" t="n"/>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="F102" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv3</t>
+          <t>발굴 산출량 Lv3</t>
         </is>
       </c>
       <c r="G102" s="30" t="n"/>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="F103" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv4</t>
+          <t>발굴 산출량 Lv4</t>
         </is>
       </c>
       <c r="G103" s="30" t="n"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv5</t>
+          <t>발굴 산출량 Lv5</t>
         </is>
       </c>
       <c r="G104" s="30" t="n"/>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="F105" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv6</t>
+          <t>발굴 산출량 Lv6</t>
         </is>
       </c>
       <c r="G105" s="30" t="n"/>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv7</t>
+          <t>발굴 산출량 Lv7</t>
         </is>
       </c>
       <c r="G106" s="30" t="n"/>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F107" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv8</t>
+          <t>발굴 산출량 Lv8</t>
         </is>
       </c>
       <c r="G107" s="30" t="n"/>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv9</t>
+          <t>발굴 산출량 Lv9</t>
         </is>
       </c>
       <c r="G108" s="30" t="n"/>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="F109" s="28" t="inlineStr">
         <is>
-          <t>낚시 산출량 Lv10</t>
+          <t>발굴 산출량 Lv10</t>
         </is>
       </c>
       <c r="G109" s="30" t="n"/>

--- a/GameDesign/Excel/User.xlsx
+++ b/GameDesign/Excel/User.xlsx
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2232,12 +2232,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
@@ -3161,12 +3161,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -6258,6 +6258,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/User.xlsx
+++ b/GameDesign/Excel/User.xlsx
@@ -414,11 +414,6 @@
         <t>이 레벨에 도달하는 데 필요한 경험치 (직전 레벨에서 · Lv1은 0)</t>
       </text>
     </comment>
-    <comment ref="D2" authorId="0" shapeId="0">
-      <text>
-        <t>이 레벨에 도달하면 주는 적성 포인트 (10의 배수 레벨만 1)</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -762,12 +757,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
@@ -777,7 +772,6 @@
       <c r="B1" s="30" t="n"/>
       <c r="C1" s="30" t="n"/>
       <c r="D1" s="30" t="n"/>
-      <c r="E1" s="30" t="n"/>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -797,11 +791,6 @@
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>특성 포인트</t>
-        </is>
-      </c>
-      <c r="E2" s="23" t="inlineStr">
-        <is>
           <t>메모</t>
         </is>
       </c>
@@ -827,11 +816,6 @@
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -851,11 +835,6 @@
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
@@ -872,10 +851,7 @@
       <c r="C5" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -886,7 +862,6 @@
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -896,8 +871,7 @@
       </c>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -916,11 +890,6 @@
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>TraitPoint</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -934,10 +903,7 @@
       <c r="C9" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>시작 레벨</t>
         </is>
@@ -951,10 +917,7 @@
       <c r="C10" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="D10" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="30" t="inlineStr"/>
+      <c r="D10" s="30" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="30" t="n"/>
@@ -964,10 +927,7 @@
       <c r="C11" s="27" t="n">
         <v>96</v>
       </c>
-      <c r="D11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="30" t="inlineStr"/>
+      <c r="D11" s="30" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="30" t="n"/>
@@ -977,10 +937,7 @@
       <c r="C12" s="27" t="n">
         <v>112</v>
       </c>
-      <c r="D12" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="30" t="inlineStr"/>
+      <c r="D12" s="30" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="30" t="n"/>
@@ -990,10 +947,7 @@
       <c r="C13" s="27" t="n">
         <v>136</v>
       </c>
-      <c r="D13" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="30" t="n"/>
@@ -1003,10 +957,7 @@
       <c r="C14" s="27" t="n">
         <v>160</v>
       </c>
-      <c r="D14" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="30" t="inlineStr"/>
+      <c r="D14" s="30" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="30" t="n"/>
@@ -1016,10 +967,7 @@
       <c r="C15" s="27" t="n">
         <v>192</v>
       </c>
-      <c r="D15" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="30" t="inlineStr"/>
+      <c r="D15" s="30" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="30" t="n"/>
@@ -1029,10 +977,7 @@
       <c r="C16" s="27" t="n">
         <v>232</v>
       </c>
-      <c r="D16" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="30" t="inlineStr"/>
+      <c r="D16" s="30" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="30" t="n"/>
@@ -1042,10 +987,7 @@
       <c r="C17" s="27" t="n">
         <v>280</v>
       </c>
-      <c r="D17" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="30" t="inlineStr"/>
+      <c r="D17" s="30" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="30" t="n"/>
@@ -1055,10 +997,7 @@
       <c r="C18" s="27" t="n">
         <v>336</v>
       </c>
-      <c r="D18" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="28" t="n"/>
+      <c r="D18" s="28" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="30" t="n"/>
@@ -1068,10 +1007,7 @@
       <c r="C19" s="27" t="n">
         <v>408</v>
       </c>
-      <c r="D19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="30" t="inlineStr"/>
+      <c r="D19" s="30" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="30" t="n"/>
@@ -1081,10 +1017,7 @@
       <c r="C20" s="27" t="n">
         <v>488</v>
       </c>
-      <c r="D20" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="30" t="inlineStr"/>
+      <c r="D20" s="30" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="30" t="n"/>
@@ -1094,10 +1027,7 @@
       <c r="C21" s="27" t="n">
         <v>592</v>
       </c>
-      <c r="D21" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="30" t="inlineStr"/>
+      <c r="D21" s="30" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="30" t="n"/>
@@ -1107,10 +1037,7 @@
       <c r="C22" s="27" t="n">
         <v>712</v>
       </c>
-      <c r="D22" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="30" t="inlineStr"/>
+      <c r="D22" s="30" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="30" t="n"/>
@@ -1120,10 +1047,7 @@
       <c r="C23" s="27" t="n">
         <v>848</v>
       </c>
-      <c r="D23" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="30" t="n"/>
@@ -1133,10 +1057,7 @@
       <c r="C24" s="27" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="30" t="inlineStr"/>
+      <c r="D24" s="30" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="30" t="n"/>
@@ -1146,10 +1067,7 @@
       <c r="C25" s="27" t="n">
         <v>1232</v>
       </c>
-      <c r="D25" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="30" t="inlineStr"/>
+      <c r="D25" s="30" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="30" t="n"/>
@@ -1159,10 +1077,7 @@
       <c r="C26" s="27" t="n">
         <v>1472</v>
       </c>
-      <c r="D26" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="30" t="inlineStr"/>
+      <c r="D26" s="30" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="30" t="n"/>
@@ -1172,10 +1087,7 @@
       <c r="C27" s="27" t="n">
         <v>1768</v>
       </c>
-      <c r="D27" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="30" t="inlineStr"/>
+      <c r="D27" s="30" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="30" t="n"/>
@@ -1185,10 +1097,7 @@
       <c r="C28" s="27" t="n">
         <v>2128</v>
       </c>
-      <c r="D28" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="30" t="n"/>
@@ -1198,10 +1107,7 @@
       <c r="C29" s="27" t="n">
         <v>2552</v>
       </c>
-      <c r="D29" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="30" t="inlineStr"/>
+      <c r="D29" s="30" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="30" t="n"/>
@@ -1211,10 +1117,7 @@
       <c r="C30" s="27" t="n">
         <v>3064</v>
       </c>
-      <c r="D30" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="30" t="inlineStr"/>
+      <c r="D30" s="30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="30" t="n"/>
@@ -1224,10 +1127,7 @@
       <c r="C31" s="27" t="n">
         <v>3680</v>
       </c>
-      <c r="D31" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="30" t="inlineStr"/>
+      <c r="D31" s="30" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="30" t="n"/>
@@ -1237,10 +1137,7 @@
       <c r="C32" s="27" t="n">
         <v>4416</v>
       </c>
-      <c r="D32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="30" t="inlineStr"/>
+      <c r="D32" s="30" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="30" t="n"/>
@@ -1250,10 +1147,7 @@
       <c r="C33" s="27" t="n">
         <v>5296</v>
       </c>
-      <c r="D33" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="28" t="n"/>
+      <c r="D33" s="28" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="30" t="n"/>
@@ -1263,10 +1157,7 @@
       <c r="C34" s="27" t="n">
         <v>6352</v>
       </c>
-      <c r="D34" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="30" t="inlineStr"/>
+      <c r="D34" s="30" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="30" t="n"/>
@@ -1276,10 +1167,7 @@
       <c r="C35" s="27" t="n">
         <v>7624</v>
       </c>
-      <c r="D35" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="30" t="inlineStr"/>
+      <c r="D35" s="30" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="30" t="n"/>
@@ -1289,10 +1177,7 @@
       <c r="C36" s="27" t="n">
         <v>9152</v>
       </c>
-      <c r="D36" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="30" t="inlineStr"/>
+      <c r="D36" s="30" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="30" t="n"/>
@@ -1302,10 +1187,7 @@
       <c r="C37" s="27" t="n">
         <v>10984</v>
       </c>
-      <c r="D37" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="30" t="inlineStr"/>
+      <c r="D37" s="30" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="30" t="n"/>
@@ -1315,10 +1197,7 @@
       <c r="C38" s="27" t="n">
         <v>13184</v>
       </c>
-      <c r="D38" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="30" t="n"/>
@@ -1328,10 +1207,7 @@
       <c r="C39" s="27" t="n">
         <v>15824</v>
       </c>
-      <c r="D39" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="30" t="inlineStr"/>
+      <c r="D39" s="30" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="30" t="n"/>
@@ -1341,10 +1217,7 @@
       <c r="C40" s="27" t="n">
         <v>18984</v>
       </c>
-      <c r="D40" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="30" t="inlineStr"/>
+      <c r="D40" s="30" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="30" t="n"/>
@@ -1354,10 +1227,7 @@
       <c r="C41" s="27" t="n">
         <v>22784</v>
       </c>
-      <c r="D41" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="30" t="inlineStr"/>
+      <c r="D41" s="30" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="30" t="n"/>
@@ -1367,10 +1237,7 @@
       <c r="C42" s="27" t="n">
         <v>27344</v>
       </c>
-      <c r="D42" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="30" t="inlineStr"/>
+      <c r="D42" s="30" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="30" t="n"/>
@@ -1380,10 +1247,7 @@
       <c r="C43" s="27" t="n">
         <v>32808</v>
       </c>
-      <c r="D43" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="30" t="n"/>
@@ -1393,10 +1257,7 @@
       <c r="C44" s="27" t="n">
         <v>39376</v>
       </c>
-      <c r="D44" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="30" t="inlineStr"/>
+      <c r="D44" s="30" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="30" t="n"/>
@@ -1406,10 +1267,7 @@
       <c r="C45" s="27" t="n">
         <v>47248</v>
       </c>
-      <c r="D45" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="30" t="inlineStr"/>
+      <c r="D45" s="30" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="30" t="n"/>
@@ -1419,10 +1277,7 @@
       <c r="C46" s="27" t="n">
         <v>56704</v>
       </c>
-      <c r="D46" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="30" t="inlineStr"/>
+      <c r="D46" s="30" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="30" t="n"/>
@@ -1432,10 +1287,7 @@
       <c r="C47" s="27" t="n">
         <v>68040</v>
       </c>
-      <c r="D47" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="30" t="inlineStr"/>
+      <c r="D47" s="30" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="30" t="n"/>
@@ -1445,10 +1297,7 @@
       <c r="C48" s="27" t="n">
         <v>81648</v>
       </c>
-      <c r="D48" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="30" t="n"/>
@@ -1458,10 +1307,7 @@
       <c r="C49" s="27" t="n">
         <v>97984</v>
       </c>
-      <c r="D49" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="30" t="inlineStr"/>
+      <c r="D49" s="30" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="30" t="n"/>
@@ -1471,10 +1317,7 @@
       <c r="C50" s="27" t="n">
         <v>117576</v>
       </c>
-      <c r="D50" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="30" t="inlineStr"/>
+      <c r="D50" s="30" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="30" t="n"/>
@@ -1484,10 +1327,7 @@
       <c r="C51" s="27" t="n">
         <v>141096</v>
       </c>
-      <c r="D51" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="30" t="inlineStr"/>
+      <c r="D51" s="30" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="30" t="n"/>
@@ -1497,10 +1337,7 @@
       <c r="C52" s="27" t="n">
         <v>169312</v>
       </c>
-      <c r="D52" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="30" t="inlineStr"/>
+      <c r="D52" s="30" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="30" t="n"/>
@@ -1510,10 +1347,7 @@
       <c r="C53" s="27" t="n">
         <v>203176</v>
       </c>
-      <c r="D53" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="28" t="n"/>
+      <c r="D53" s="28" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="30" t="n"/>
@@ -1523,10 +1357,7 @@
       <c r="C54" s="27" t="n">
         <v>243816</v>
       </c>
-      <c r="D54" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="30" t="inlineStr"/>
+      <c r="D54" s="30" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="30" t="n"/>
@@ -1536,10 +1367,7 @@
       <c r="C55" s="27" t="n">
         <v>292576</v>
       </c>
-      <c r="D55" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="30" t="inlineStr"/>
+      <c r="D55" s="30" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="30" t="n"/>
@@ -1549,10 +1377,7 @@
       <c r="C56" s="27" t="n">
         <v>351096</v>
       </c>
-      <c r="D56" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="30" t="inlineStr"/>
+      <c r="D56" s="30" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="30" t="n"/>
@@ -1562,10 +1387,7 @@
       <c r="C57" s="27" t="n">
         <v>421312</v>
       </c>
-      <c r="D57" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="30" t="inlineStr"/>
+      <c r="D57" s="30" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="30" t="n"/>
@@ -1575,10 +1397,7 @@
       <c r="C58" s="27" t="n">
         <v>505576</v>
       </c>
-      <c r="D58" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="28" t="n"/>
+      <c r="D58" s="28" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="30" t="n"/>
@@ -1588,10 +1407,7 @@
       <c r="C59" s="27" t="n">
         <v>606688</v>
       </c>
-      <c r="D59" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="30" t="inlineStr"/>
+      <c r="D59" s="30" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="30" t="n"/>
@@ -1601,10 +1417,7 @@
       <c r="C60" s="27" t="n">
         <v>728032</v>
       </c>
-      <c r="D60" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="30" t="inlineStr"/>
+      <c r="D60" s="30" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="30" t="n"/>
@@ -1614,10 +1427,7 @@
       <c r="C61" s="27" t="n">
         <v>873640</v>
       </c>
-      <c r="D61" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="30" t="inlineStr"/>
+      <c r="D61" s="30" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="30" t="n"/>
@@ -1627,10 +1437,7 @@
       <c r="C62" s="27" t="n">
         <v>1048368</v>
       </c>
-      <c r="D62" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="30" t="inlineStr"/>
+      <c r="D62" s="30" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="30" t="n"/>
@@ -1640,10 +1447,7 @@
       <c r="C63" s="27" t="n">
         <v>1258040</v>
       </c>
-      <c r="D63" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="28" t="n"/>
+      <c r="D63" s="28" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="30" t="n"/>
@@ -1653,10 +1457,7 @@
       <c r="C64" s="27" t="n">
         <v>1509648</v>
       </c>
-      <c r="D64" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="30" t="inlineStr"/>
+      <c r="D64" s="30" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="30" t="n"/>
@@ -1666,10 +1467,7 @@
       <c r="C65" s="27" t="n">
         <v>1811584</v>
       </c>
-      <c r="D65" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="30" t="inlineStr"/>
+      <c r="D65" s="30" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="30" t="n"/>
@@ -1679,10 +1477,7 @@
       <c r="C66" s="27" t="n">
         <v>2173896</v>
       </c>
-      <c r="D66" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="30" t="inlineStr"/>
+      <c r="D66" s="30" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="30" t="n"/>
@@ -1692,10 +1487,7 @@
       <c r="C67" s="27" t="n">
         <v>2608680</v>
       </c>
-      <c r="D67" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="30" t="inlineStr"/>
+      <c r="D67" s="30" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="30" t="n"/>
@@ -1705,10 +1497,7 @@
       <c r="C68" s="27" t="n">
         <v>3130416</v>
       </c>
-      <c r="D68" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="28" t="n"/>
+      <c r="D68" s="28" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="30" t="n"/>
@@ -1718,10 +1507,7 @@
       <c r="C69" s="27" t="n">
         <v>3756496</v>
       </c>
-      <c r="D69" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="30" t="inlineStr"/>
+      <c r="D69" s="30" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="30" t="n"/>
@@ -1731,10 +1517,7 @@
       <c r="C70" s="27" t="n">
         <v>4507800</v>
       </c>
-      <c r="D70" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="30" t="inlineStr"/>
+      <c r="D70" s="30" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="30" t="n"/>
@@ -1744,10 +1527,7 @@
       <c r="C71" s="27" t="n">
         <v>5409360</v>
       </c>
-      <c r="D71" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="30" t="inlineStr"/>
+      <c r="D71" s="30" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="30" t="n"/>
@@ -1757,10 +1537,7 @@
       <c r="C72" s="27" t="n">
         <v>6491232</v>
       </c>
-      <c r="D72" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="30" t="inlineStr"/>
+      <c r="D72" s="30" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="30" t="n"/>
@@ -1770,10 +1547,7 @@
       <c r="C73" s="27" t="n">
         <v>7789480</v>
       </c>
-      <c r="D73" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="28" t="n"/>
+      <c r="D73" s="28" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="30" t="n"/>
@@ -1783,10 +1557,7 @@
       <c r="C74" s="27" t="n">
         <v>9347376</v>
       </c>
-      <c r="D74" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="30" t="inlineStr"/>
+      <c r="D74" s="30" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="30" t="n"/>
@@ -1796,10 +1567,7 @@
       <c r="C75" s="27" t="n">
         <v>11216848</v>
       </c>
-      <c r="D75" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="30" t="inlineStr"/>
+      <c r="D75" s="30" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="30" t="n"/>
@@ -1809,10 +1577,7 @@
       <c r="C76" s="27" t="n">
         <v>13460216</v>
       </c>
-      <c r="D76" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="30" t="inlineStr"/>
+      <c r="D76" s="30" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="30" t="n"/>
@@ -1822,10 +1587,7 @@
       <c r="C77" s="27" t="n">
         <v>16152264</v>
       </c>
-      <c r="D77" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="30" t="inlineStr"/>
+      <c r="D77" s="30" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="30" t="n"/>
@@ -1835,10 +1597,7 @@
       <c r="C78" s="27" t="n">
         <v>19382712</v>
       </c>
-      <c r="D78" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="28" t="n"/>
+      <c r="D78" s="28" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="30" t="n"/>
@@ -1848,10 +1607,7 @@
       <c r="C79" s="27" t="n">
         <v>23259256</v>
       </c>
-      <c r="D79" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="30" t="inlineStr"/>
+      <c r="D79" s="30" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="30" t="n"/>
@@ -1861,10 +1617,7 @@
       <c r="C80" s="27" t="n">
         <v>27911112</v>
       </c>
-      <c r="D80" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="30" t="inlineStr"/>
+      <c r="D80" s="30" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="30" t="n"/>
@@ -1874,10 +1627,7 @@
       <c r="C81" s="27" t="n">
         <v>33493336</v>
       </c>
-      <c r="D81" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="30" t="inlineStr"/>
+      <c r="D81" s="30" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="30" t="n"/>
@@ -1887,10 +1637,7 @@
       <c r="C82" s="27" t="n">
         <v>40192000</v>
       </c>
-      <c r="D82" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="30" t="inlineStr"/>
+      <c r="D82" s="30" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="30" t="n"/>
@@ -1900,10 +1647,7 @@
       <c r="C83" s="27" t="n">
         <v>48230408</v>
       </c>
-      <c r="D83" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="28" t="n"/>
+      <c r="D83" s="28" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="30" t="n"/>
@@ -1913,10 +1657,7 @@
       <c r="C84" s="27" t="n">
         <v>57876488</v>
       </c>
-      <c r="D84" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="30" t="inlineStr"/>
+      <c r="D84" s="30" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="30" t="n"/>
@@ -1926,10 +1667,7 @@
       <c r="C85" s="27" t="n">
         <v>69451784</v>
       </c>
-      <c r="D85" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="30" t="inlineStr"/>
+      <c r="D85" s="30" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="30" t="n"/>
@@ -1939,10 +1677,7 @@
       <c r="C86" s="27" t="n">
         <v>83342144</v>
       </c>
-      <c r="D86" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="30" t="inlineStr"/>
+      <c r="D86" s="30" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="30" t="n"/>
@@ -1952,10 +1687,7 @@
       <c r="C87" s="27" t="n">
         <v>100010576</v>
       </c>
-      <c r="D87" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="30" t="inlineStr"/>
+      <c r="D87" s="30" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="30" t="n"/>
@@ -1965,10 +1697,7 @@
       <c r="C88" s="27" t="n">
         <v>120012688</v>
       </c>
-      <c r="D88" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="28" t="n"/>
+      <c r="D88" s="28" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="30" t="n"/>
@@ -1978,10 +1707,7 @@
       <c r="C89" s="27" t="n">
         <v>144015224</v>
       </c>
-      <c r="D89" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="30" t="inlineStr"/>
+      <c r="D89" s="30" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="30" t="n"/>
@@ -1991,10 +1717,7 @@
       <c r="C90" s="27" t="n">
         <v>172818272</v>
       </c>
-      <c r="D90" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="30" t="inlineStr"/>
+      <c r="D90" s="30" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="30" t="n"/>
@@ -2004,10 +1727,7 @@
       <c r="C91" s="27" t="n">
         <v>207381928</v>
       </c>
-      <c r="D91" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="30" t="inlineStr"/>
+      <c r="D91" s="30" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="30" t="n"/>
@@ -2017,10 +1737,7 @@
       <c r="C92" s="27" t="n">
         <v>248858312</v>
       </c>
-      <c r="D92" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="30" t="inlineStr"/>
+      <c r="D92" s="30" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="30" t="n"/>
@@ -2030,10 +1747,7 @@
       <c r="C93" s="27" t="n">
         <v>298629976</v>
       </c>
-      <c r="D93" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="28" t="n"/>
+      <c r="D93" s="28" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="30" t="n"/>
@@ -2043,10 +1757,7 @@
       <c r="C94" s="27" t="n">
         <v>358355976</v>
       </c>
-      <c r="D94" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="30" t="inlineStr"/>
+      <c r="D94" s="30" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="30" t="n"/>
@@ -2056,10 +1767,7 @@
       <c r="C95" s="27" t="n">
         <v>430027168</v>
       </c>
-      <c r="D95" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="30" t="inlineStr"/>
+      <c r="D95" s="30" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="30" t="n"/>
@@ -2069,10 +1777,7 @@
       <c r="C96" s="27" t="n">
         <v>516032608</v>
       </c>
-      <c r="D96" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="30" t="inlineStr"/>
+      <c r="D96" s="30" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="30" t="n"/>
@@ -2082,10 +1787,7 @@
       <c r="C97" s="27" t="n">
         <v>619239128</v>
       </c>
-      <c r="D97" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="30" t="inlineStr"/>
+      <c r="D97" s="30" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="30" t="n"/>
@@ -2095,10 +1797,7 @@
       <c r="C98" s="27" t="n">
         <v>743086952</v>
       </c>
-      <c r="D98" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="28" t="n"/>
+      <c r="D98" s="28" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="30" t="n"/>
@@ -2108,10 +1807,7 @@
       <c r="C99" s="27" t="n">
         <v>891704344</v>
       </c>
-      <c r="D99" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="30" t="inlineStr"/>
+      <c r="D99" s="30" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="30" t="n"/>
@@ -2121,10 +1817,7 @@
       <c r="C100" s="27" t="n">
         <v>1070045216</v>
       </c>
-      <c r="D100" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="30" t="inlineStr"/>
+      <c r="D100" s="30" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="30" t="n"/>
@@ -2134,10 +1827,7 @@
       <c r="C101" s="27" t="n">
         <v>1284054256</v>
       </c>
-      <c r="D101" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="30" t="inlineStr"/>
+      <c r="D101" s="30" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="30" t="n"/>
@@ -2147,10 +1837,7 @@
       <c r="C102" s="27" t="n">
         <v>1540865112</v>
       </c>
-      <c r="D102" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="30" t="inlineStr"/>
+      <c r="D102" s="30" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="30" t="n"/>
@@ -2160,10 +1847,7 @@
       <c r="C103" s="27" t="n">
         <v>1849038136</v>
       </c>
-      <c r="D103" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="28" t="n"/>
+      <c r="D103" s="28" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="30" t="n"/>
@@ -2173,10 +1857,7 @@
       <c r="C104" s="27" t="n">
         <v>2218845768</v>
       </c>
-      <c r="D104" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="30" t="inlineStr"/>
+      <c r="D104" s="30" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="30" t="n"/>
@@ -2186,10 +1867,7 @@
       <c r="C105" s="27" t="n">
         <v>2662614920</v>
       </c>
-      <c r="D105" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="30" t="inlineStr"/>
+      <c r="D105" s="30" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="30" t="n"/>
@@ -2199,10 +1877,7 @@
       <c r="C106" s="27" t="n">
         <v>3195137904</v>
       </c>
-      <c r="D106" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="30" t="inlineStr"/>
+      <c r="D106" s="30" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="30" t="n"/>
@@ -2212,10 +1887,7 @@
       <c r="C107" s="27" t="n">
         <v>3834165480</v>
       </c>
-      <c r="D107" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="30" t="inlineStr"/>
+      <c r="D107" s="30" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="30" t="n"/>
@@ -2225,10 +1897,507 @@
       <c r="C108" s="27" t="n">
         <v>4600998584</v>
       </c>
-      <c r="D108" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="28" t="n"/>
+      <c r="D108" s="28" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="30" t="n"/>
+      <c r="B109" s="27" t="n">
+        <v>101</v>
+      </c>
+      <c r="C109" s="27" t="n">
+        <v>5521198301</v>
+      </c>
+      <c r="D109" s="30" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="30" t="n"/>
+      <c r="B110" s="27" t="n">
+        <v>102</v>
+      </c>
+      <c r="C110" s="27" t="n">
+        <v>6625437961</v>
+      </c>
+      <c r="D110" s="30" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="30" t="n"/>
+      <c r="B111" s="27" t="n">
+        <v>103</v>
+      </c>
+      <c r="C111" s="27" t="n">
+        <v>7950525553</v>
+      </c>
+      <c r="D111" s="30" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="30" t="n"/>
+      <c r="B112" s="27" t="n">
+        <v>104</v>
+      </c>
+      <c r="C112" s="27" t="n">
+        <v>9540630664</v>
+      </c>
+      <c r="D112" s="30" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="30" t="n"/>
+      <c r="B113" s="27" t="n">
+        <v>105</v>
+      </c>
+      <c r="C113" s="27" t="n">
+        <v>11448756797</v>
+      </c>
+      <c r="D113" s="30" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="30" t="n"/>
+      <c r="B114" s="27" t="n">
+        <v>106</v>
+      </c>
+      <c r="C114" s="27" t="n">
+        <v>13738508156</v>
+      </c>
+      <c r="D114" s="30" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="30" t="n"/>
+      <c r="B115" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="C115" s="27" t="n">
+        <v>16486209787</v>
+      </c>
+      <c r="D115" s="30" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="30" t="n"/>
+      <c r="B116" s="27" t="n">
+        <v>108</v>
+      </c>
+      <c r="C116" s="27" t="n">
+        <v>19783451744</v>
+      </c>
+      <c r="D116" s="30" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="n"/>
+      <c r="B117" s="27" t="n">
+        <v>109</v>
+      </c>
+      <c r="C117" s="27" t="n">
+        <v>23740142093</v>
+      </c>
+      <c r="D117" s="30" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="30" t="n"/>
+      <c r="B118" s="27" t="n">
+        <v>110</v>
+      </c>
+      <c r="C118" s="27" t="n">
+        <v>28488170512</v>
+      </c>
+      <c r="D118" s="30" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="30" t="n"/>
+      <c r="B119" s="27" t="n">
+        <v>111</v>
+      </c>
+      <c r="C119" s="27" t="n">
+        <v>34185804614</v>
+      </c>
+      <c r="D119" s="30" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="30" t="n"/>
+      <c r="B120" s="27" t="n">
+        <v>112</v>
+      </c>
+      <c r="C120" s="27" t="n">
+        <v>41022965537</v>
+      </c>
+      <c r="D120" s="30" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="30" t="n"/>
+      <c r="B121" s="27" t="n">
+        <v>113</v>
+      </c>
+      <c r="C121" s="27" t="n">
+        <v>49227558644</v>
+      </c>
+      <c r="D121" s="30" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="30" t="n"/>
+      <c r="B122" s="27" t="n">
+        <v>114</v>
+      </c>
+      <c r="C122" s="27" t="n">
+        <v>59073070373</v>
+      </c>
+      <c r="D122" s="30" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="30" t="n"/>
+      <c r="B123" s="27" t="n">
+        <v>115</v>
+      </c>
+      <c r="C123" s="27" t="n">
+        <v>70887684448</v>
+      </c>
+      <c r="D123" s="30" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="30" t="n"/>
+      <c r="B124" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="C124" s="27" t="n">
+        <v>85065221338</v>
+      </c>
+      <c r="D124" s="30" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="30" t="n"/>
+      <c r="B125" s="27" t="n">
+        <v>117</v>
+      </c>
+      <c r="C125" s="27" t="n">
+        <v>102078265606</v>
+      </c>
+      <c r="D125" s="30" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="30" t="n"/>
+      <c r="B126" s="27" t="n">
+        <v>118</v>
+      </c>
+      <c r="C126" s="27" t="n">
+        <v>122493918727</v>
+      </c>
+      <c r="D126" s="30" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="30" t="n"/>
+      <c r="B127" s="27" t="n">
+        <v>119</v>
+      </c>
+      <c r="C127" s="27" t="n">
+        <v>146992702472</v>
+      </c>
+      <c r="D127" s="30" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="30" t="n"/>
+      <c r="B128" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="C128" s="27" t="n">
+        <v>176391242966</v>
+      </c>
+      <c r="D128" s="30" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="30" t="n"/>
+      <c r="B129" s="27" t="n">
+        <v>121</v>
+      </c>
+      <c r="C129" s="27" t="n">
+        <v>211669491559</v>
+      </c>
+      <c r="D129" s="30" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="30" t="n"/>
+      <c r="B130" s="27" t="n">
+        <v>122</v>
+      </c>
+      <c r="C130" s="27" t="n">
+        <v>254003389871</v>
+      </c>
+      <c r="D130" s="30" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="30" t="n"/>
+      <c r="B131" s="27" t="n">
+        <v>123</v>
+      </c>
+      <c r="C131" s="27" t="n">
+        <v>304804067845</v>
+      </c>
+      <c r="D131" s="30" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="30" t="n"/>
+      <c r="B132" s="27" t="n">
+        <v>124</v>
+      </c>
+      <c r="C132" s="27" t="n">
+        <v>365764881414</v>
+      </c>
+      <c r="D132" s="30" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="n"/>
+      <c r="B133" s="27" t="n">
+        <v>125</v>
+      </c>
+      <c r="C133" s="27" t="n">
+        <v>438917857697</v>
+      </c>
+      <c r="D133" s="30" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="n"/>
+      <c r="B134" s="27" t="n">
+        <v>126</v>
+      </c>
+      <c r="C134" s="27" t="n">
+        <v>526701429236</v>
+      </c>
+      <c r="D134" s="30" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="30" t="n"/>
+      <c r="B135" s="27" t="n">
+        <v>127</v>
+      </c>
+      <c r="C135" s="27" t="n">
+        <v>632041715083</v>
+      </c>
+      <c r="D135" s="30" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="30" t="n"/>
+      <c r="B136" s="27" t="n">
+        <v>128</v>
+      </c>
+      <c r="C136" s="27" t="n">
+        <v>758450058100</v>
+      </c>
+      <c r="D136" s="30" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="30" t="n"/>
+      <c r="B137" s="27" t="n">
+        <v>129</v>
+      </c>
+      <c r="C137" s="27" t="n">
+        <v>910140069720</v>
+      </c>
+      <c r="D137" s="30" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="30" t="n"/>
+      <c r="B138" s="27" t="n">
+        <v>130</v>
+      </c>
+      <c r="C138" s="27" t="n">
+        <v>1092168083664</v>
+      </c>
+      <c r="D138" s="30" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="30" t="n"/>
+      <c r="B139" s="27" t="n">
+        <v>131</v>
+      </c>
+      <c r="C139" s="27" t="n">
+        <v>1310601700397</v>
+      </c>
+      <c r="D139" s="30" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="30" t="n"/>
+      <c r="B140" s="27" t="n">
+        <v>132</v>
+      </c>
+      <c r="C140" s="27" t="n">
+        <v>1572722040476</v>
+      </c>
+      <c r="D140" s="30" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="30" t="n"/>
+      <c r="B141" s="27" t="n">
+        <v>133</v>
+      </c>
+      <c r="C141" s="27" t="n">
+        <v>1887266448571</v>
+      </c>
+      <c r="D141" s="30" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="30" t="n"/>
+      <c r="B142" s="27" t="n">
+        <v>134</v>
+      </c>
+      <c r="C142" s="27" t="n">
+        <v>2264719738285</v>
+      </c>
+      <c r="D142" s="30" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="30" t="n"/>
+      <c r="B143" s="27" t="n">
+        <v>135</v>
+      </c>
+      <c r="C143" s="27" t="n">
+        <v>2717663685942</v>
+      </c>
+      <c r="D143" s="30" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="30" t="n"/>
+      <c r="B144" s="27" t="n">
+        <v>136</v>
+      </c>
+      <c r="C144" s="27" t="n">
+        <v>3261196423130</v>
+      </c>
+      <c r="D144" s="30" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="30" t="n"/>
+      <c r="B145" s="27" t="n">
+        <v>137</v>
+      </c>
+      <c r="C145" s="27" t="n">
+        <v>3913435707756</v>
+      </c>
+      <c r="D145" s="30" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="30" t="n"/>
+      <c r="B146" s="27" t="n">
+        <v>138</v>
+      </c>
+      <c r="C146" s="27" t="n">
+        <v>4696122849307</v>
+      </c>
+      <c r="D146" s="30" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="30" t="n"/>
+      <c r="B147" s="27" t="n">
+        <v>139</v>
+      </c>
+      <c r="C147" s="27" t="n">
+        <v>5635347419168</v>
+      </c>
+      <c r="D147" s="30" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="30" t="n"/>
+      <c r="B148" s="27" t="n">
+        <v>140</v>
+      </c>
+      <c r="C148" s="27" t="n">
+        <v>6762416903002</v>
+      </c>
+      <c r="D148" s="30" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="30" t="n"/>
+      <c r="B149" s="27" t="n">
+        <v>141</v>
+      </c>
+      <c r="C149" s="27" t="n">
+        <v>8114900283602</v>
+      </c>
+      <c r="D149" s="30" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="30" t="n"/>
+      <c r="B150" s="27" t="n">
+        <v>142</v>
+      </c>
+      <c r="C150" s="27" t="n">
+        <v>9737880340322</v>
+      </c>
+      <c r="D150" s="30" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="30" t="n"/>
+      <c r="B151" s="27" t="n">
+        <v>143</v>
+      </c>
+      <c r="C151" s="27" t="n">
+        <v>11685456408386</v>
+      </c>
+      <c r="D151" s="30" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="30" t="n"/>
+      <c r="B152" s="27" t="n">
+        <v>144</v>
+      </c>
+      <c r="C152" s="27" t="n">
+        <v>14022547690063</v>
+      </c>
+      <c r="D152" s="30" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="30" t="n"/>
+      <c r="B153" s="27" t="n">
+        <v>145</v>
+      </c>
+      <c r="C153" s="27" t="n">
+        <v>16827057228076</v>
+      </c>
+      <c r="D153" s="30" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="30" t="n"/>
+      <c r="B154" s="27" t="n">
+        <v>146</v>
+      </c>
+      <c r="C154" s="27" t="n">
+        <v>20192468673691</v>
+      </c>
+      <c r="D154" s="30" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="30" t="n"/>
+      <c r="B155" s="27" t="n">
+        <v>147</v>
+      </c>
+      <c r="C155" s="27" t="n">
+        <v>24230962408429</v>
+      </c>
+      <c r="D155" s="30" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="30" t="n"/>
+      <c r="B156" s="27" t="n">
+        <v>148</v>
+      </c>
+      <c r="C156" s="27" t="n">
+        <v>29077154890115</v>
+      </c>
+      <c r="D156" s="30" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="30" t="n"/>
+      <c r="B157" s="27" t="n">
+        <v>149</v>
+      </c>
+      <c r="C157" s="27" t="n">
+        <v>34892585868138</v>
+      </c>
+      <c r="D157" s="30" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="30" t="n"/>
+      <c r="B158" s="27" t="n">
+        <v>150</v>
+      </c>
+      <c r="C158" s="27" t="n">
+        <v>41871103041766</v>
+      </c>
+      <c r="D158" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2242,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2254,7 +2423,11 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2268,6 +2441,10 @@
       <c r="H1" s="30" t="n"/>
       <c r="I1" s="30" t="n"/>
       <c r="J1" s="30" t="n"/>
+      <c r="K1" s="30" t="n"/>
+      <c r="L1" s="30" t="n"/>
+      <c r="M1" s="30" t="n"/>
+      <c r="N1" s="30" t="n"/>
     </row>
     <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="31" t="inlineStr">
@@ -2317,6 +2494,26 @@
       </c>
       <c r="J2" s="33" t="inlineStr">
         <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="K2" s="33" t="inlineStr">
+        <is>
+          <t>열</t>
+        </is>
+      </c>
+      <c r="L2" s="33" t="inlineStr">
+        <is>
+          <t>줄</t>
+        </is>
+      </c>
+      <c r="M2" s="33" t="inlineStr">
+        <is>
+          <t>선행 노드</t>
+        </is>
+      </c>
+      <c r="N2" s="33" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -2372,6 +2569,26 @@
           <t>a</t>
         </is>
       </c>
+      <c r="K3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="L3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="M3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="N3" s="34" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="31" t="inlineStr">
@@ -2420,6 +2637,26 @@
         </is>
       </c>
       <c r="J4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L4" s="34" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M4" s="34" t="inlineStr">
+        <is>
+          <t>int[]</t>
+        </is>
+      </c>
+      <c r="N4" s="34" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2449,7 +2686,17 @@
       <c r="I5" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="34" t="n"/>
+      <c r="J5" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="34" t="n"/>
+      <c r="N5" s="34" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="31" t="inlineStr">
@@ -2466,6 +2713,10 @@
       <c r="H6" s="34" t="n"/>
       <c r="I6" s="34" t="n"/>
       <c r="J6" s="34" t="n"/>
+      <c r="K6" s="34" t="n"/>
+      <c r="L6" s="34" t="n"/>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="34" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
@@ -2481,7 +2732,15 @@
       <c r="G7" s="34" t="n"/>
       <c r="H7" s="34" t="n"/>
       <c r="I7" s="34" t="n"/>
-      <c r="J7" s="34" t="inlineStr">
+      <c r="J7" s="34" t="n"/>
+      <c r="K7" s="34" t="n"/>
+      <c r="L7" s="34" t="n"/>
+      <c r="M7" s="34" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="N7" s="34" t="inlineStr">
         <is>
           <t>""</t>
         </is>
@@ -2501,7 +2760,19 @@
       <c r="G8" s="34" t="n"/>
       <c r="H8" s="34" t="n"/>
       <c r="I8" s="34" t="n"/>
-      <c r="J8" s="34" t="n"/>
+      <c r="J8" s="34" t="inlineStr">
+        <is>
+          <t>BuildingTable.BuildingTID</t>
+        </is>
+      </c>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="34" t="inlineStr">
+        <is>
+          <t>UserTraitTable.UserTraitTID?</t>
+        </is>
+      </c>
+      <c r="N8" s="34" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="32" t="n"/>
@@ -2546,6 +2817,26 @@
         </is>
       </c>
       <c r="J9" s="36" t="inlineStr">
+        <is>
+          <t>BuildingTID</t>
+        </is>
+      </c>
+      <c r="K9" s="36" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="L9" s="36" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="M9" s="36" t="inlineStr">
+        <is>
+          <t>RequiredTraitTIDs</t>
+        </is>
+      </c>
+      <c r="N9" s="36" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -2583,7 +2874,17 @@
       <c r="I10" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="30" t="n"/>
+      <c r="N10" s="28" t="inlineStr">
         <is>
           <t>농사 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
@@ -2621,7 +2922,17 @@
       <c r="I11" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="30" t="n"/>
+      <c r="N11" s="28" t="inlineStr">
         <is>
           <t>발굴 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
@@ -2659,7 +2970,17 @@
       <c r="I12" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="28" t="inlineStr">
         <is>
           <t>채굴 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
@@ -2697,7 +3018,17 @@
       <c r="I13" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="28" t="inlineStr">
+      <c r="J13" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="30" t="n"/>
+      <c r="N13" s="28" t="inlineStr">
         <is>
           <t>벌목 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
@@ -2735,7 +3066,17 @@
       <c r="I14" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="28" t="inlineStr">
+      <c r="J14" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="30" t="n"/>
+      <c r="N14" s="28" t="inlineStr">
         <is>
           <t>사냥 산업 레벨 해금 — 특성 레벨 = 열린 산업 레벨</t>
         </is>
@@ -2773,7 +3114,21 @@
       <c r="I15" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J15" s="28" t="inlineStr">
+      <c r="J15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="28" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="N15" s="28" t="inlineStr">
         <is>
           <t>농사 작업속도 레벨당 +5% (테스트값)</t>
         </is>
@@ -2811,7 +3166,21 @@
       <c r="I16" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J16" s="28" t="inlineStr">
+      <c r="J16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="28" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>발굴 작업속도 레벨당 +5% (테스트값)</t>
         </is>
@@ -2849,7 +3218,21 @@
       <c r="I17" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J17" s="28" t="inlineStr">
+      <c r="J17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="28" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N17" s="28" t="inlineStr">
         <is>
           <t>채굴 작업속도 레벨당 +5% (테스트값)</t>
         </is>
@@ -2887,7 +3270,21 @@
       <c r="I18" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J18" s="28" t="inlineStr">
+      <c r="J18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="28" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N18" s="28" t="inlineStr">
         <is>
           <t>벌목 작업속도 레벨당 +5% (테스트값)</t>
         </is>
@@ -2925,7 +3322,21 @@
       <c r="I19" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="28" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="28" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N19" s="28" t="inlineStr">
         <is>
           <t>사냥 작업속도 레벨당 +5% (테스트값)</t>
         </is>
@@ -2963,7 +3374,17 @@
       <c r="I20" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="28" t="inlineStr">
+      <c r="J20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n"/>
+      <c r="N20" s="28" t="inlineStr">
         <is>
           <t>전 산업 산출량 레벨당 +2% (테스트값)</t>
         </is>
@@ -3001,7 +3422,21 @@
       <c r="I21" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J21" s="28" t="inlineStr">
+      <c r="J21" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="28" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="N21" s="28" t="inlineStr">
         <is>
           <t>농사 산출량 레벨당 +5% (테스트값)</t>
         </is>
@@ -3039,7 +3474,21 @@
       <c r="I22" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="28" t="inlineStr">
+      <c r="J22" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" s="28" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="N22" s="28" t="inlineStr">
         <is>
           <t>발굴 산출량 레벨당 +5% (테스트값)</t>
         </is>
@@ -3077,7 +3526,21 @@
       <c r="I23" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J23" s="28" t="inlineStr">
+      <c r="J23" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M23" s="28" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="N23" s="28" t="inlineStr">
         <is>
           <t>채굴 산출량 레벨당 +5% (테스트값)</t>
         </is>
@@ -3115,7 +3578,21 @@
       <c r="I24" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J24" s="28" t="inlineStr">
+      <c r="J24" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" s="28" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="N24" s="28" t="inlineStr">
         <is>
           <t>벌목 산출량 레벨당 +5% (테스트값)</t>
         </is>
@@ -3153,7 +3630,21 @@
       <c r="I25" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="J25" s="28" t="inlineStr">
+      <c r="J25" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="28" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="N25" s="28" t="inlineStr">
         <is>
           <t>사냥 산출량 레벨당 +5% (테스트값)</t>
         </is>
